--- a/POS_UAT_Test_Plan.xlsx
+++ b/POS_UAT_Test_Plan.xlsx
@@ -13,12 +13,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1223" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1745" uniqueCount="872">
   <si>
     <t>GEORGE MUNICIPALITY — POS RECEIPTING SYSTEM UAT TEST PLAN</t>
   </si>
   <si>
-    <t>Test Date: ___/___/______    Version: 1.0    Environment: UAT (Platinum Inzalo EMS API)</t>
+    <t>Test Date: ___/___/______    Version: 2.0    Environment: UAT (Platinum Inzalo EMS API)</t>
   </si>
   <si>
     <t>Agent (Auto)</t>
@@ -81,7 +81,7 @@
 4. Click Login</t>
   </si>
   <si>
-    <t>Login succeeds. User redirected to POS screen. userId and finYear returned. Session cookie set.</t>
+    <t>Login succeeds. userId and finYear returned. Session cookie set. Redirected to POS.</t>
   </si>
   <si>
     <t>PASS</t>
@@ -99,7 +99,7 @@
     <t>Session status check</t>
   </si>
   <si>
-    <t>1. After login, check session status via API /api/auth/status</t>
+    <t>1. After login, check /api/auth/status</t>
   </si>
   <si>
     <t>Returns authenticated=true with user details.</t>
@@ -111,11 +111,11 @@
     <t>Ensure cashier (auto-setup)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. After login, system calls ensure-cashier
-2. Verify cashierId and officeId returned</t>
-  </si>
-  <si>
-    <t>cashierId=33338, officeId=1 returned. Cashier session initialized.</t>
+    <t xml:space="preserve">1. System calls ensure-cashier after login
+2. Verify cashierId and officeId</t>
+  </si>
+  <si>
+    <t>cashierId=33338, officeId=1 returned.</t>
   </si>
   <si>
     <t>TC-004</t>
@@ -124,10 +124,10 @@
     <t>Session blocked banner (no session)</t>
   </si>
   <si>
-    <t>1. Navigate to /pos without active cashier session</t>
-  </si>
-  <si>
-    <t>"No Active Cashier Session" banner displays with "Go to Cashier Setup" button.</t>
+    <t>1. Navigate to /pos without active session</t>
+  </si>
+  <si>
+    <t>"No Active Cashier Session" banner with "Go to Cashier Setup" button.</t>
   </si>
   <si>
     <t>TC-005</t>
@@ -136,11 +136,11 @@
     <t>Session active indicator</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Login and complete cashier setup
-2. Check header subtitle area</t>
-  </si>
-  <si>
-    <t>Green "Session Active" badge appears next to cashier name and office.</t>
+    <t xml:space="preserve">1. Login and setup cashier
+2. Check header</t>
+  </si>
+  <si>
+    <t>Green "Session Active" badge next to cashier name/office.</t>
   </si>
   <si>
     <t>TC-006</t>
@@ -149,11 +149,11 @@
     <t>Day-End pending approval state</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Submit day-end reconciliation
-2. Before supervisor approves, revisit /pos</t>
-  </si>
-  <si>
-    <t>"Day-End Pending Approval" banner shows. POS transactions disabled.</t>
+    <t xml:space="preserve">1. Submit day-end
+2. Revisit /pos before approval</t>
+  </si>
+  <si>
+    <t>"Day-End Pending Approval" banner. Transactions disabled.</t>
   </si>
   <si>
     <t>TC-007</t>
@@ -166,7 +166,7 @@
 2. Cashier revisits /pos</t>
   </si>
   <si>
-    <t>"Day-End Returned" banner with decline reason. "Go to Cashier Setup" button shown.</t>
+    <t>"Day-End Returned" banner with decline reason.</t>
   </si>
   <si>
     <t>TC-008</t>
@@ -175,1499 +175,2203 @@
     <t>Reconciliation required state</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Cashier session requires reconciliation
+    <t xml:space="preserve">1. Session requires reconciliation
 2. Visit /pos</t>
   </si>
   <si>
-    <t>"Reconciliation Required" banner with "Go to Day-End Reconciliation" button.</t>
+    <t>"Reconciliation Required" banner with "Go to Day-End" button.</t>
   </si>
   <si>
     <t>TC-009</t>
   </si>
   <si>
-    <t>2. Search &amp; Lookups</t>
+    <t>Logout and session cleanup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Click logout
+2. Try accessing protected routes</t>
+  </si>
+  <si>
+    <t>Session cleared. Redirected to login page.</t>
+  </si>
+  <si>
+    <t>TC-010</t>
+  </si>
+  <si>
+    <t>2. Cashier Setup</t>
+  </si>
+  <si>
+    <t>Cashier registration check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to Cashier Setup
+2. System checks if user is registered cashier</t>
+  </si>
+  <si>
+    <t>Step 1 shows success if registered. Shows error if not registered.</t>
+  </si>
+  <si>
+    <t>TC-011</t>
+  </si>
+  <si>
+    <t>Cash office list loads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. View Cashier Setup
+2. Check cash office dropdown</t>
+  </si>
+  <si>
+    <t>Dropdown populated with available cash offices from API.</t>
+  </si>
+  <si>
+    <t>TC-012</t>
+  </si>
+  <si>
+    <t>Select cash office</t>
+  </si>
+  <si>
+    <t>1. Select a different cash office from dropdown</t>
+  </si>
+  <si>
+    <t>Office changes. SCOA/vote code updates. Payment options reload.</t>
+  </si>
+  <si>
+    <t>TC-013</t>
+  </si>
+  <si>
+    <t>Float amount entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter opening float amount (e.g. R500)
+2. Verify display</t>
+  </si>
+  <si>
+    <t>Float input accepts value. Pre-populated from user profile if available.</t>
+  </si>
+  <si>
+    <t>TC-014</t>
+  </si>
+  <si>
+    <t>Payment options loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. After office selection
+2. View payment options section</t>
+  </si>
+  <si>
+    <t>Shows enabled payment options (Consumer, Clearance, Prepaid, Misc) with tick marks.</t>
+  </si>
+  <si>
+    <t>TC-015</t>
+  </si>
+  <si>
+    <t>Payment types loaded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. After office selection
+2. View payment types section</t>
+  </si>
+  <si>
+    <t>Shows enabled payment types (Cash, Credit Card) with tick marks.</t>
+  </si>
+  <si>
+    <t>TC-016</t>
+  </si>
+  <si>
+    <t>Receipt range validation</t>
+  </si>
+  <si>
+    <t>1. Setup checks receipt range via validate-receipt-range</t>
+  </si>
+  <si>
+    <t>Receipt range status displayed. Warning if range exhausted.</t>
+  </si>
+  <si>
+    <t>TC-017</t>
+  </si>
+  <si>
+    <t>Start new session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Fill all setup fields
+2. Click Start Session</t>
+  </si>
+  <si>
+    <t>Cashier session started via submit-cashier-setup. Success message. Redirected to POS.</t>
+  </si>
+  <si>
+    <t>TC-018</t>
+  </si>
+  <si>
+    <t>Resume existing session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. User has active session
+2. Visit Cashier Setup</t>
+  </si>
+  <si>
+    <t>"Active Session" indicator. "Resume Session" option available. No duplicate session created.</t>
+  </si>
+  <si>
+    <t>TC-019</t>
+  </si>
+  <si>
+    <t>Day-end pending blocks new session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Previous day-end pending approval
+2. Try to start new session</t>
+  </si>
+  <si>
+    <t>Error: "Your day-end reconciliation is pending supervisor approval." Cannot start.</t>
+  </si>
+  <si>
+    <t>TC-020</t>
+  </si>
+  <si>
+    <t>Non-default office warning</t>
+  </si>
+  <si>
+    <t>1. Select an office different from default</t>
+  </si>
+  <si>
+    <t>Warning indicator shown that selected office differs from default.</t>
+  </si>
+  <si>
+    <t>TC-021</t>
+  </si>
+  <si>
+    <t>3. Search &amp; Lookups</t>
   </si>
   <si>
     <t>Dynamic search by account number</t>
   </si>
   <si>
-    <t xml:space="preserve">1. In Dynamic Search mode
-2. Type account number (e.g. "16360")
+    <t xml:space="preserve">1. Dynamic Search mode
+2. Type "16360"
 3. Click Search</t>
   </si>
   <si>
-    <t>Returns matching accounts with name, address, balance, account number, status badge.</t>
-  </si>
-  <si>
-    <t>TC-010</t>
+    <t>Returns matching accounts with name, address, balance, status badge.</t>
+  </si>
+  <si>
+    <t>TC-022</t>
   </si>
   <si>
     <t>Dynamic search by name</t>
   </si>
   <si>
-    <t xml:space="preserve">1. In Dynamic Search mode
-2. Type customer name (e.g. "Crawford")
+    <t xml:space="preserve">1. Dynamic Search mode
+2. Type "Crawford"
 3. Click Search</t>
   </si>
   <si>
-    <t>Returns matching accounts. Shows account details (name, address, balance).</t>
-  </si>
-  <si>
-    <t>TC-011</t>
+    <t>Returns matching accounts by name.</t>
+  </si>
+  <si>
+    <t>TC-023</t>
   </si>
   <si>
     <t>Tab-based account search</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Switch to Category Tabs mode
-2. Select Account tab
-3. Enter search term and click Search</t>
-  </si>
-  <si>
-    <t>Returns results with same parallel dual-endpoint approach (search-accounts + search-account-groups). Deduplicated by account ID.</t>
-  </si>
-  <si>
-    <t>TC-012</t>
-  </si>
-  <si>
-    <t>Search with no results</t>
-  </si>
-  <si>
-    <t>1. Search for non-existent account "ZZZZZ99999"</t>
-  </si>
-  <si>
-    <t>"No results found matching your search" message displayed.</t>
-  </si>
-  <si>
-    <t>TC-013</t>
-  </si>
-  <si>
-    <t>Account group search and expand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Search returns group results
-2. Click on a group result
-3. View expanded accounts</t>
-  </si>
-  <si>
-    <t>Group expands showing all accounts within. "Add All to Basket" button visible. Each account shows name, number, balance.</t>
-  </si>
-  <si>
-    <t>TC-014</t>
-  </si>
-  <si>
-    <t>Add all group accounts to basket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Expand a group
+    <t xml:space="preserve">1. Category Tabs → Account tab
+2. Enter search and click Search</t>
+  </si>
+  <si>
+    <t>Uses dual-endpoint parallel search (search-accounts + search-account-groups). Deduplicated by account ID.</t>
+  </si>
+  <si>
+    <t>TC-024</t>
+  </si>
+  <si>
+    <t>Search no results</t>
+  </si>
+  <si>
+    <t>1. Search "ZZZZZ99999"</t>
+  </si>
+  <si>
+    <t>"No results found" message.</t>
+  </si>
+  <si>
+    <t>TC-025</t>
+  </si>
+  <si>
+    <t>Account group expand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search returns group
+2. Click to expand</t>
+  </si>
+  <si>
+    <t>Group expands showing accounts. "Add All to Basket" button visible.</t>
+  </si>
+  <si>
+    <t>TC-026</t>
+  </si>
+  <si>
+    <t>Add all group accounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Expand group
 2. Click "Add All to Basket"</t>
   </si>
   <si>
-    <t>All accounts in group added to basket. Each shows correct due amount.</t>
-  </si>
-  <si>
-    <t>TC-015</t>
+    <t>All group accounts added to basket.</t>
+  </si>
+  <si>
+    <t>TC-027</t>
   </si>
   <si>
     <t>Misc payment groups load</t>
   </si>
   <si>
-    <t>1. Call /api/platinum/billing-payment-miscellaneous/get-groups</t>
-  </si>
-  <si>
-    <t>Returns list of misc payment groups with groupId and groupName.</t>
-  </si>
-  <si>
-    <t>TC-016</t>
+    <t>1. Call get-groups endpoint</t>
+  </si>
+  <si>
+    <t>Returns misc payment groups with groupId and groupName.</t>
+  </si>
+  <si>
+    <t>TC-028</t>
   </si>
   <si>
     <t>SCOA items for misc group</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Select a misc payment group
+    <t xml:space="preserve">1. Select misc group
 2. System loads SCOA items</t>
   </si>
   <si>
-    <t>Returns SCOA items with scoaItemId, scoaItemName, isVatable, vatPercentage.</t>
-  </si>
-  <si>
-    <t>TC-017</t>
+    <t>Returns SCOA items with isVatable, vatPercentage.</t>
+  </si>
+  <si>
+    <t>TC-029</t>
   </si>
   <si>
     <t>Payment types/options</t>
   </si>
   <si>
-    <t>1. Query cashier payment types and options</t>
-  </si>
-  <si>
-    <t>Returns valid payment types (Cash=1, Card=3). Only cash, card, cash+card allowed.</t>
-  </si>
-  <si>
-    <t>TC-018</t>
+    <t>1. Query cashier payment types</t>
+  </si>
+  <si>
+    <t>Returns Cash=1, Card=3. Only cash, card, cash+card allowed.</t>
+  </si>
+  <si>
+    <t>TC-030</t>
   </si>
   <si>
     <t>Clear search results</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Perform a search
-2. Click Clear/close button</t>
-  </si>
-  <si>
-    <t>Search results panel dismissed. Query cleared.</t>
-  </si>
-  <si>
-    <t>TC-019</t>
-  </si>
-  <si>
-    <t>Prepaid service types load</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Switch to Prepaid tab
+    <t xml:space="preserve">1. Perform search
+2. Click Clear</t>
+  </si>
+  <si>
+    <t>Results dismissed. Query cleared.</t>
+  </si>
+  <si>
+    <t>TC-031</t>
+  </si>
+  <si>
+    <t>Prepaid service types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Prepaid tab
 2. View service type dropdown</t>
   </si>
   <si>
-    <t>Dropdown populated with available service types from API.</t>
-  </si>
-  <si>
-    <t>TC-020</t>
-  </si>
-  <si>
-    <t>Inline prepaid shortcut from account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Search returns account with prepaid meter
-2. Account result shows "Add Prepaid Electricity" button</t>
-  </si>
-  <si>
-    <t>Button shows meter number. Clicking adds prepaid item to basket with meter pre-filled.</t>
-  </si>
-  <si>
-    <t>TC-021</t>
-  </si>
-  <si>
-    <t>3. Basket Management</t>
-  </si>
-  <si>
-    <t>Add account to basket from search</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Search for account
-2. Click on account result</t>
-  </si>
-  <si>
-    <t>Account added to basket with correct label, description, due amount. Type badge shows "CONSUMER".</t>
-  </si>
-  <si>
-    <t>TC-022</t>
+    <t>Populated with available service types.</t>
+  </si>
+  <si>
+    <t>TC-032</t>
+  </si>
+  <si>
+    <t>Inline prepaid from account</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Account with prepaid meter in results
+2. Click "Add Prepaid Electricity" button</t>
+  </si>
+  <si>
+    <t>Prepaid item added with meter pre-filled.</t>
+  </si>
+  <si>
+    <t>TC-033</t>
+  </si>
+  <si>
+    <t>4. Basket Management</t>
+  </si>
+  <si>
+    <t>Add account to basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search account
+2. Click result</t>
+  </si>
+  <si>
+    <t>Added with correct label, due amount, type badge "CONSUMER".</t>
+  </si>
+  <si>
+    <t>TC-034</t>
   </si>
   <si>
     <t>Add clearance to basket</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Switch to Clearance tab
-2. Enter clearance ID
-3. Click Search</t>
-  </si>
-  <si>
-    <t>Clearance certificate found and added to basket. Shows owner name, status, account count.</t>
-  </si>
-  <si>
-    <t>TC-023</t>
+    <t xml:space="preserve">1. Clearance tab
+2. Enter ID, Search</t>
+  </si>
+  <si>
+    <t>Clearance added. Shows owner, status, accounts.</t>
+  </si>
+  <si>
+    <t>TC-035</t>
   </si>
   <si>
     <t>Add prepaid to basket</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Switch to Prepaid tab
-2. Enter meter number and amount
-3. Click "Get Breakdown &amp; Add"</t>
-  </si>
-  <si>
-    <t>Prepaid breakdown retrieved. Item added to basket showing service type and meter number.</t>
-  </si>
-  <si>
-    <t>TC-024</t>
-  </si>
-  <si>
-    <t>Add misc to basket (tab form)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Switch to Misc tab
-2. Select payment group and SCOA item
-3. Enter last name, initials, amount, description
-4. Click "Add to Basket"</t>
-  </si>
-  <si>
-    <t>Misc item added to basket. Form disappears (switches to account mode). Item shows group name, SCOA item.</t>
-  </si>
-  <si>
-    <t>TC-025</t>
-  </si>
-  <si>
-    <t>Misc form auto-collapse after add</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add misc item via tab form
-2. Observe tab state</t>
-  </si>
-  <si>
-    <t>After adding, activeMode switches to "account" — misc form disappears automatically.</t>
-  </si>
-  <si>
-    <t>TC-026</t>
+    <t xml:space="preserve">1. Prepaid tab
+2. Enter meter + amount
+3. Get Breakdown &amp; Add</t>
+  </si>
+  <si>
+    <t>Prepaid breakdown retrieved. Added to basket.</t>
+  </si>
+  <si>
+    <t>TC-036</t>
+  </si>
+  <si>
+    <t>Add misc to basket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Misc tab
+2. Select group/SCOA
+3. Enter details
+4. Add to Basket</t>
+  </si>
+  <si>
+    <t>Misc added. Form auto-collapses (switches to account mode).</t>
+  </si>
+  <si>
+    <t>TC-037</t>
   </si>
   <si>
     <t>Edit basket item amount</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add account to basket
-2. Enter custom amount in "Pay" field</t>
-  </si>
-  <si>
-    <t>Amount updates correctly. Payment summary totals recalculate.</t>
-  </si>
-  <si>
-    <t>TC-027</t>
+    <t xml:space="preserve">1. Add account
+2. Enter custom pay amount</t>
+  </si>
+  <si>
+    <t>Amount updates. Summary totals recalculate.</t>
+  </si>
+  <si>
+    <t>TC-038</t>
   </si>
   <si>
     <t>Pay Full Amount button</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add account with balance &gt; 0
-2. Click "FULL" button next to pay input</t>
-  </si>
-  <si>
-    <t>Pay amount set to full outstanding balance.</t>
-  </si>
-  <si>
-    <t>TC-028</t>
+    <t xml:space="preserve">1. Account with balance &gt; 0
+2. Click "FULL"</t>
+  </si>
+  <si>
+    <t>Pay amount set to full outstanding.</t>
+  </si>
+  <si>
+    <t>TC-039</t>
   </si>
   <si>
     <t>Pay All Full button</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add multiple items to basket
+    <t xml:space="preserve">1. Multiple items
 2. Click "Pay All Full"</t>
   </si>
   <si>
-    <t>All items set to their full due amounts. Total recalculates.</t>
-  </si>
-  <si>
-    <t>TC-029</t>
+    <t>All items set to full due. Totals recalculate.</t>
+  </si>
+  <si>
+    <t>TC-040</t>
   </si>
   <si>
     <t>Remove item from basket</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add items to basket
-2. Click X (remove) button on an item</t>
-  </si>
-  <si>
-    <t>Item removed. Basket count decreases. Totals recalculate.</t>
-  </si>
-  <si>
-    <t>TC-030</t>
+    <t>1. Click X on item</t>
+  </si>
+  <si>
+    <t>Item removed. Count decreases. Totals recalculate.</t>
+  </si>
+  <si>
+    <t>TC-041</t>
   </si>
   <si>
     <t>Clear All basket</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add multiple items to basket
-2. Click "Clear All"</t>
-  </si>
-  <si>
-    <t>All items removed. Empty basket state shown ("Ready for Transactions").</t>
-  </si>
-  <si>
-    <t>TC-031</t>
-  </si>
-  <si>
-    <t>Empty basket state display</t>
-  </si>
-  <si>
-    <t>1. Clear all items from basket</t>
-  </si>
-  <si>
-    <t>Shopping cart icon with "Ready for Transactions" text and instruction text.</t>
-  </si>
-  <si>
-    <t>TC-032</t>
-  </si>
-  <si>
-    <t>Mixed basket (multi-type)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add account + clearance + prepaid + misc items
-2. View basket</t>
-  </si>
-  <si>
-    <t>All four types shown with correct colour-coded type badges. Processing order numbers displayed (1=Consumer, 2=Clearance, 3=Prepaid, 4=Misc).</t>
-  </si>
-  <si>
-    <t>TC-033</t>
-  </si>
-  <si>
-    <t>Edit misc payer details inline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add misc item to basket
-2. Edit last name/initials fields inline in basket</t>
-  </si>
-  <si>
-    <t>Inline fields (last name, initials) update the misc item data.</t>
-  </si>
-  <si>
-    <t>TC-034</t>
-  </si>
-  <si>
-    <t>Credit balance account display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Search for account with credit balance (negative)
-2. Add to basket</t>
-  </si>
-  <si>
-    <t>Balance shown in green with "Credit" badge. Due amount shows negative.</t>
-  </si>
-  <si>
-    <t>TC-035</t>
-  </si>
-  <si>
-    <t>Account status badge display</t>
-  </si>
-  <si>
-    <t>1. Add active and inactive accounts</t>
-  </si>
-  <si>
-    <t>Active accounts show green "Active" badge. Inactive show red badge.</t>
-  </si>
-  <si>
-    <t>TC-036</t>
-  </si>
-  <si>
-    <t>Prepaid button from basket account</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add account with prepaid meter to basket
-2. Click "Prepaid Electricity: [meter]" chip</t>
-  </si>
-  <si>
-    <t>Prepaid form opens pre-filled with meter number from account.</t>
-  </si>
-  <si>
-    <t>TC-037</t>
-  </si>
-  <si>
-    <t>4. Payment Summary</t>
-  </si>
-  <si>
-    <t>Summary shows correct totals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add multiple items to basket
-2. View Payment Summary panel on right</t>
-  </si>
-  <si>
-    <t>Item count, Total Due, and Total to Pay display correctly. Each type section shows items with subtotals.</t>
-  </si>
-  <si>
-    <t>TC-038</t>
-  </si>
-  <si>
-    <t>Summary grouped by type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add items of different types
-2. View summary breakdown</t>
-  </si>
-  <si>
-    <t>Consumer, Clearance, Prepaid, Misc sections each show their items with colour dots and subtotals.</t>
-  </si>
-  <si>
-    <t>TC-039</t>
+    <t>1. Click "Clear All"</t>
+  </si>
+  <si>
+    <t>All removed. Empty state shown.</t>
+  </si>
+  <si>
+    <t>TC-042</t>
+  </si>
+  <si>
+    <t>Mixed basket (all 4 types)</t>
+  </si>
+  <si>
+    <t>1. Add account + clearance + prepaid + misc</t>
+  </si>
+  <si>
+    <t>All shown with colour-coded badges and processing order numbers.</t>
+  </si>
+  <si>
+    <t>TC-043</t>
+  </si>
+  <si>
+    <t>Edit misc payer inline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add misc
+2. Edit last name/initials inline</t>
+  </si>
+  <si>
+    <t>Inline fields update misc item data.</t>
+  </si>
+  <si>
+    <t>TC-044</t>
+  </si>
+  <si>
+    <t>Credit balance account</t>
+  </si>
+  <si>
+    <t>1. Add account with credit balance</t>
+  </si>
+  <si>
+    <t>Green balance with "Credit" badge. Negative due.</t>
+  </si>
+  <si>
+    <t>TC-045</t>
+  </si>
+  <si>
+    <t>Account status badge</t>
+  </si>
+  <si>
+    <t>1. Add active/inactive accounts</t>
+  </si>
+  <si>
+    <t>Active=green badge, Inactive=red badge.</t>
+  </si>
+  <si>
+    <t>TC-046</t>
+  </si>
+  <si>
+    <t>5. Payment Summary</t>
+  </si>
+  <si>
+    <t>Summary totals correct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add items
+2. View right panel</t>
+  </si>
+  <si>
+    <t>Item count, Total Due, Total to Pay correct. Type sections with subtotals.</t>
+  </si>
+  <si>
+    <t>TC-047</t>
   </si>
   <si>
     <t>Processing order legend</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add items to basket
-2. View "Processing Order" section below summary</t>
-  </si>
-  <si>
-    <t>Legend shows: 1. Consumer (blue), 2. Clearance (green), 3. Prepaid (orange), 4. Misc (purple).</t>
-  </si>
-  <si>
-    <t>TC-040</t>
-  </si>
-  <si>
-    <t>Process Payment button disabled when empty</t>
-  </si>
-  <si>
-    <t>1. Clear basket or have zero amounts</t>
-  </si>
-  <si>
-    <t>Process Payment button disabled. Cannot click.</t>
-  </si>
-  <si>
-    <t>TC-041</t>
-  </si>
-  <si>
-    <t>Process Payment button disabled when zero amount items</t>
-  </si>
-  <si>
-    <t>1. Add item but leave pay amount at 0</t>
-  </si>
-  <si>
-    <t>Button disabled. Cannot proceed with zero-amount items.</t>
-  </si>
-  <si>
-    <t>TC-042</t>
-  </si>
-  <si>
-    <t>5. Payment Tender</t>
+    <t xml:space="preserve">1. Add items
+2. View legend</t>
+  </si>
+  <si>
+    <t>1=Consumer(blue), 2=Clearance(green), 3=Prepaid(orange), 4=Misc(purple).</t>
+  </si>
+  <si>
+    <t>TC-048</t>
+  </si>
+  <si>
+    <t>Process button disabled (empty)</t>
+  </si>
+  <si>
+    <t>1. Empty basket or zero amounts</t>
+  </si>
+  <si>
+    <t>Button disabled.</t>
+  </si>
+  <si>
+    <t>TC-049</t>
+  </si>
+  <si>
+    <t>6. Payment Tender</t>
   </si>
   <si>
     <t>Open payment panel</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add items with valid amounts
+    <t xml:space="preserve">1. Add items
 2. Click "Process Payment"</t>
   </si>
   <si>
-    <t>Payment tender overlay opens. Shows amount due. Tender type tabs visible.</t>
-  </si>
-  <si>
-    <t>TC-043</t>
+    <t>Overlay opens. Amount due shown. Tender tabs visible.</t>
+  </si>
+  <si>
+    <t>TC-050</t>
   </si>
   <si>
     <t>Cash tender — enter amount</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Select Cash tab
-2. Enter cash amount in input</t>
-  </si>
-  <si>
-    <t>Cash amount updates. Change calculated if overpayment.</t>
-  </si>
-  <si>
-    <t>TC-044</t>
+    <t xml:space="preserve">1. Cash tab
+2. Enter amount</t>
+  </si>
+  <si>
+    <t>Cash updates. Change calculated if overpay.</t>
+  </si>
+  <si>
+    <t>TC-051</t>
   </si>
   <si>
     <t>Cash denomination buttons</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Select Cash tab
-2. Click denomination buttons (R10, R20, R50, etc.)</t>
-  </si>
-  <si>
-    <t>Cash amount increments by denomination value. Correct buttons shown for all denominations.</t>
-  </si>
-  <si>
-    <t>TC-045</t>
-  </si>
-  <si>
-    <t>Cash exact amount button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select Cash tab
-2. Click "Exact Amount (Rounded)"</t>
-  </si>
-  <si>
-    <t>Cash set to exact rounded amount (nearest 10c). No change.</t>
-  </si>
-  <si>
-    <t>TC-046</t>
-  </si>
-  <si>
-    <t>Cash rounding (SA 10c rule)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Total amount = R15.03
-2. Select cash tender</t>
-  </si>
-  <si>
-    <t>Amount rounded to R15.00 (nearest 10c). Rounding indicator shows "rounded down by 3c".</t>
-  </si>
-  <si>
-    <t>TC-047</t>
-  </si>
-  <si>
-    <t>Cash rounding (round up)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Total amount = R15.07
-2. Select cash tender</t>
-  </si>
-  <si>
-    <t>Amount rounded to R15.10 (nearest 10c). Rounding indicator shows "rounded up".</t>
-  </si>
-  <si>
-    <t>TC-048</t>
-  </si>
-  <si>
-    <t>Card tender — enter details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select Card tab
-2. Enter card amount, card number, expiry, reference</t>
-  </si>
-  <si>
-    <t>All fields accept input. Card amount set. Card number formatted with spaces.</t>
-  </si>
-  <si>
-    <t>TC-049</t>
-  </si>
-  <si>
-    <t>Card tender — no change allowed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Select Card tab
-2. Enter card amount &gt; total due</t>
-  </si>
-  <si>
-    <t>Card overpay warning shown. Change amount = 0 (card payments have no cash change).</t>
-  </si>
-  <si>
-    <t>TC-050</t>
+    <t xml:space="preserve">1. Cash tab
+2. Click R10, R20, R50, etc.</t>
+  </si>
+  <si>
+    <t>Amount increments by denomination.</t>
+  </si>
+  <si>
+    <t>TC-052</t>
+  </si>
+  <si>
+    <t>Cash exact amount</t>
+  </si>
+  <si>
+    <t>1. Click "Exact Amount (Rounded)"</t>
+  </si>
+  <si>
+    <t>Set to exact rounded amount. No change.</t>
+  </si>
+  <si>
+    <t>TC-053</t>
+  </si>
+  <si>
+    <t>Cash rounding (10c SA rule)</t>
+  </si>
+  <si>
+    <t>1. Total R15.03 → cash</t>
+  </si>
+  <si>
+    <t>Rounded to R15.00. Rounding indicator shows.</t>
+  </si>
+  <si>
+    <t>TC-054</t>
+  </si>
+  <si>
+    <t>Card tender — full details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Card tab
+2. Enter card amount, number, expiry, ref</t>
+  </si>
+  <si>
+    <t>All fields accept input. Card number formatted.</t>
+  </si>
+  <si>
+    <t>TC-055</t>
+  </si>
+  <si>
+    <t>Card — no change</t>
+  </si>
+  <si>
+    <t>1. Card overpay</t>
+  </si>
+  <si>
+    <t>Card overpay warning. Change = 0.</t>
+  </si>
+  <si>
+    <t>TC-056</t>
   </si>
   <si>
     <t>Cash+Card split tender</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Select Cash+Card tab
+    <t xml:space="preserve">1. Cash+Card tab
 2. Enter cash portion
-3. Card portion auto-calculates (or manual)</t>
-  </si>
-  <si>
-    <t>Split view shows Cash and Card columns. Combined total matches due amount. Cash/Card summary shows both portions.</t>
-  </si>
-  <si>
-    <t>TC-051</t>
-  </si>
-  <si>
-    <t>Cash+Card — cash denomination buttons</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. In Cash+Card mode
-2. Click cash denomination buttons</t>
-  </si>
-  <si>
-    <t>Cash portion increments. Card portion adjusts to cover remainder.</t>
-  </si>
-  <si>
-    <t>TC-052</t>
-  </si>
-  <si>
-    <t>Cash+Card — smart allocation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Set cash=R50, card=R30 for R80 total
-2. Submit payment</t>
-  </si>
-  <si>
-    <t>Creates separate receipts per tender type per item. Cash receipt and card receipt generated separately.</t>
-  </si>
-  <si>
-    <t>TC-053</t>
-  </si>
-  <si>
-    <t>Change cap R200 enforcement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Total due = R50
-2. Enter cash = R300 (change = R250)</t>
-  </si>
-  <si>
-    <t>Validation error: "Change cannot exceed R200". Submit button disabled.</t>
-  </si>
-  <si>
-    <t>TC-054</t>
+3. Card auto-calculates</t>
+  </si>
+  <si>
+    <t>Split view. Combined matches due. Summary shows both.</t>
+  </si>
+  <si>
+    <t>TC-057</t>
+  </si>
+  <si>
+    <t>Cash+Card denomination buttons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Cash+Card mode
+2. Click denomination</t>
+  </si>
+  <si>
+    <t>Cash increments. Card adjusts remainder.</t>
+  </si>
+  <si>
+    <t>TC-058</t>
+  </si>
+  <si>
+    <t>Change cap R200</t>
+  </si>
+  <si>
+    <t>1. Due R50, Cash R300 (change R250)</t>
+  </si>
+  <si>
+    <t>"Change cannot exceed R200". Submit disabled.</t>
+  </si>
+  <si>
+    <t>TC-059</t>
   </si>
   <si>
     <t>Change R200 boundary (valid)</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Total due = R50
-2. Enter cash = R250 (change = R200)</t>
-  </si>
-  <si>
-    <t>R200 change accepted (boundary case). Submit enabled.</t>
-  </si>
-  <si>
-    <t>TC-055</t>
+    <t>1. Due R50, Cash R250 (change R200)</t>
+  </si>
+  <si>
+    <t>R200 change accepted. Submit enabled.</t>
+  </si>
+  <si>
+    <t>TC-060</t>
   </si>
   <si>
     <t>Shortfall warning</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Total due = R100
-2. Enter cash = R50</t>
-  </si>
-  <si>
-    <t>"Shortfall R50.00" warning displayed. Submit disabled until fully tendered.</t>
-  </si>
-  <si>
-    <t>TC-056</t>
-  </si>
-  <si>
-    <t>Total tendered display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter tender amounts
-2. View totals section</t>
-  </si>
-  <si>
-    <t>Shows individual amounts (Cash, Card) and Total Tendered. Change line if applicable.</t>
-  </si>
-  <si>
-    <t>TC-057</t>
+    <t>1. Due R100, Cash R50</t>
+  </si>
+  <si>
+    <t>"Shortfall R50.00" displayed. Submit disabled.</t>
+  </si>
+  <si>
+    <t>TC-061</t>
   </si>
   <si>
     <t>Close payment panel</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Open payment panel
-2. Click X button or click outside overlay</t>
-  </si>
-  <si>
-    <t>Payment panel closes. Basket preserved.</t>
-  </si>
-  <si>
-    <t>TC-058</t>
-  </si>
-  <si>
-    <t>6. Payment Submission</t>
-  </si>
-  <si>
-    <t>Single account — cash payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add account to basket
-2. Set pay amount
-3. Select Cash tender
-4. Enter cash amount
-5. Submit</t>
-  </si>
-  <si>
-    <t>Payment submitted to Platinum API. Receipt returned with receiptNo and ID. Success modal appears.</t>
-  </si>
-  <si>
-    <t>TC-059</t>
-  </si>
-  <si>
-    <t>Single account — card payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add account to basket
-2. Set pay amount
-3. Select Card tender
-4. Enter card details
-5. Submit</t>
-  </si>
-  <si>
-    <t>Payment submitted. Receipt returned. Card info masked in server logs.</t>
-  </si>
-  <si>
-    <t>TC-060</t>
-  </si>
-  <si>
-    <t>Multi-account payment (2+ accounts)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add 2 or more accounts to basket
-2. Set amounts
-3. Select tender
-4. Submit</t>
-  </si>
-  <si>
-    <t>Uses submit-multiple-payment endpoint. Returns one ID per account. Creates separate ReceiptResult for each account.</t>
-  </si>
-  <si>
-    <t>TC-061</t>
+    <t>1. Click X or outside overlay</t>
+  </si>
+  <si>
+    <t>Panel closes. Basket preserved.</t>
+  </si>
+  <si>
+    <t>TC-062</t>
+  </si>
+  <si>
+    <t>7. Payment Submission</t>
+  </si>
+  <si>
+    <t>Single account — cash</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add account
+2. Cash tender
+3. Submit</t>
+  </si>
+  <si>
+    <t>Receipt returned with receiptNo and ID.</t>
+  </si>
+  <si>
+    <t>TC-063</t>
+  </si>
+  <si>
+    <t>Single account — card</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add account
+2. Card tender
+3. Submit</t>
+  </si>
+  <si>
+    <t>Receipt returned. Card masked in server logs.</t>
+  </si>
+  <si>
+    <t>TC-064</t>
+  </si>
+  <si>
+    <t>Multi-account payment (2+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add 2+ accounts
+2. Submit</t>
+  </si>
+  <si>
+    <t>Uses submit-multiple-payment. One ID per account. Separate ReceiptResult each.</t>
+  </si>
+  <si>
+    <t>TC-065</t>
   </si>
   <si>
     <t>Misc payment submission</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add misc item to basket
-2. Set amount
-3. Select tender
-4. Submit</t>
-  </si>
-  <si>
-    <t>Uses billing-payment-miscellaneous/submit endpoint (PascalCase payload). Returns receiptNo and receipt ID.</t>
-  </si>
-  <si>
-    <t>TC-062</t>
+    <t xml:space="preserve">1. Add misc
+2. Submit</t>
+  </si>
+  <si>
+    <t>Uses billing-payment-miscellaneous/submit (PascalCase). Returns receiptNo.</t>
+  </si>
+  <si>
+    <t>TC-066</t>
   </si>
   <si>
     <t>Cash+Card split — separate receipts</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add account item
-2. Select Cash+Card tender
-3. Set cash/card portions
-4. Submit</t>
-  </si>
-  <si>
-    <t>TWO separate receipts created (one cash, one card). Each has proper tender type. API payloads separated per tender.</t>
-  </si>
-  <si>
-    <t>TC-063</t>
-  </si>
-  <si>
-    <t>Mixed basket payment (account + misc)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add account and misc items
-2. Set amounts
+    <t xml:space="preserve">1. Add account
+2. Cash+Card
 3. Submit</t>
   </si>
   <si>
-    <t>Account processed via consumer payment endpoint. Misc via miscellaneous endpoint. Separate receipt per type.</t>
-  </si>
-  <si>
-    <t>TC-064</t>
+    <t>TWO separate receipts (cash + card). Separate API payloads.</t>
+  </si>
+  <si>
+    <t>TC-067</t>
+  </si>
+  <si>
+    <t>Mixed basket (account + misc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Add account + misc
+2. Submit</t>
+  </si>
+  <si>
+    <t>Account → consumer endpoint. Misc → misc endpoint. Separate receipts.</t>
+  </si>
+  <si>
+    <t>TC-068</t>
   </si>
   <si>
     <t>Processing order enforced</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Add Consumer + Clearance + Prepaid + Misc items
-2. Submit payment</t>
-  </si>
-  <si>
-    <t>Items processed in order: Consumer first, then Clearance, Prepaid, Misc last.</t>
-  </si>
-  <si>
-    <t>TC-065</t>
-  </si>
-  <si>
-    <t>Zero amount item blocked</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Add item but leave amount at 0
-2. Try to process</t>
-  </si>
-  <si>
-    <t>Process Payment button disabled. Cannot submit zero amounts.</t>
-  </si>
-  <si>
-    <t>TC-066</t>
-  </si>
-  <si>
-    <t>Payment progress tracking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Submit payment with multiple items
-2. Observe progress display</t>
-  </si>
-  <si>
-    <t>Real-time progress indicator shows items being processed.</t>
-  </si>
-  <si>
-    <t>TC-067</t>
-  </si>
-  <si>
-    <t>7. Receipt Modal (v2)</t>
-  </si>
-  <si>
-    <t>Receipt modal appears on success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Submit any valid payment
-2. Wait for processing to complete</t>
-  </si>
-  <si>
-    <t>Receipt modal (580px wide) opens. Shows "Payment Successful" header with timestamp (dd/mm/yyyy).</t>
-  </si>
-  <si>
-    <t>TC-068</t>
-  </si>
-  <si>
-    <t>Receipt modal — total amount display</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete payment
-2. View modal summary bar</t>
-  </si>
-  <si>
-    <t>Total amount shown in large green text. Receipt count and item count displayed.</t>
+    <t xml:space="preserve">1. Add all 4 types
+2. Submit</t>
+  </si>
+  <si>
+    <t>Processed: Consumer → Clearance → Prepaid → Misc.</t>
   </si>
   <si>
     <t>TC-069</t>
   </si>
   <si>
-    <t>Receipt modal — account receipt details</t>
+    <t>Zero amount blocked</t>
+  </si>
+  <si>
+    <t>1. Leave amount at 0</t>
+  </si>
+  <si>
+    <t>Process button disabled.</t>
+  </si>
+  <si>
+    <t>TC-070</t>
+  </si>
+  <si>
+    <t>8. Receipt Modal (v2)</t>
+  </si>
+  <si>
+    <t>Modal appears on success</t>
+  </si>
+  <si>
+    <t>1. Complete any payment</t>
+  </si>
+  <si>
+    <t>580px modal. "Payment Successful". Timestamp dd/mm/yyyy.</t>
+  </si>
+  <si>
+    <t>TC-071</t>
+  </si>
+  <si>
+    <t>Total amount display</t>
+  </si>
+  <si>
+    <t>1. View modal summary bar</t>
+  </si>
+  <si>
+    <t>Large green total. Receipt + item counts.</t>
+  </si>
+  <si>
+    <t>TC-072</t>
+  </si>
+  <si>
+    <t>Account receipt details</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete account payment
-2. View receipt card in modal</t>
-  </si>
-  <si>
-    <t>Shows type badge "Consumer Payment", tender type (CASH/CARD), receipt number, account number, name, address, amount.</t>
-  </si>
-  <si>
-    <t>TC-070</t>
-  </si>
-  <si>
-    <t>Receipt modal — misc receipt details</t>
+2. View receipt card</t>
+  </si>
+  <si>
+    <t>"Consumer Payment" badge, CASH/CARD tender, receipt no, account no, name, address, amount.</t>
+  </si>
+  <si>
+    <t>TC-073</t>
+  </si>
+  <si>
+    <t>Misc receipt details</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete misc payment
-2. View receipt card in modal</t>
-  </si>
-  <si>
-    <t>Shows type badge "Miscellaneous", payment group, SCOA item, payer name/initials, description, VAT breakdown.</t>
-  </si>
-  <si>
-    <t>TC-071</t>
-  </si>
-  <si>
-    <t>Receipt modal — clearance receipt details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete clearance payment
-2. View receipt card in modal</t>
-  </si>
-  <si>
-    <t>Shows type badge "Clearance", clearance ID, owner name, property description.</t>
-  </si>
-  <si>
-    <t>TC-072</t>
-  </si>
-  <si>
-    <t>Receipt modal — prepaid receipt details</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete prepaid payment
-2. View receipt card in modal</t>
-  </si>
-  <si>
-    <t>Shows type badge "Prepaid Recharge", meter number, service type.</t>
-  </si>
-  <si>
-    <t>TC-073</t>
-  </si>
-  <si>
-    <t>Receipt modal — split payment banner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete Cash+Card split payment
-2. View receipt modal</t>
-  </si>
-  <si>
-    <t>Blue banner shows "Split Payment: Cash R xxx + Card R xxx". Multiple receipts displayed.</t>
+2. View card</t>
+  </si>
+  <si>
+    <t>"Miscellaneous" badge, group, SCOA item, payer name/initials, description, VAT.</t>
   </si>
   <si>
     <t>TC-074</t>
   </si>
   <si>
-    <t>Receipt modal — cashier/office info</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete any payment
-2. View transaction info footer</t>
-  </si>
-  <si>
-    <t>Shows cashier name (first + last, titlecase) and cash office name.</t>
+    <t>Clearance receipt details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete clearance
+2. View card</t>
+  </si>
+  <si>
+    <t>"Clearance" badge, ID, owner, property.</t>
   </si>
   <si>
     <t>TC-075</t>
   </si>
   <si>
-    <t>Receipt modal — receipt number format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete payment
-2. View receipt number in modal</t>
-  </si>
-  <si>
-    <t>Receipt number displayed in monospace font (e.g. "13032026/911082").</t>
+    <t>Prepaid receipt details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete prepaid
+2. View card</t>
+  </si>
+  <si>
+    <t>"Prepaid Recharge" badge, meter no, service type.</t>
   </si>
   <si>
     <t>TC-076</t>
   </si>
   <si>
-    <t>Receipt modal — Done button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. View receipt modal
-2. Click "Done"</t>
-  </si>
-  <si>
-    <t>Modal closes. Basket cleared. POS returns to ready state.</t>
+    <t>Split payment banner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete Cash+Card split
+2. View modal</t>
+  </si>
+  <si>
+    <t>Blue banner: "Split Payment: Cash R xxx + Card R xxx". Multiple receipts.</t>
   </si>
   <si>
     <t>TC-077</t>
   </si>
   <si>
-    <t>8. Receipt Printing</t>
+    <t>Cashier/office info footer</t>
+  </si>
+  <si>
+    <t>1. View modal footer</t>
+  </si>
+  <si>
+    <t>Cashier name (titlecase) and cash office name.</t>
+  </si>
+  <si>
+    <t>TC-078</t>
+  </si>
+  <si>
+    <t>Done button</t>
+  </si>
+  <si>
+    <t>1. Click "Done"</t>
+  </si>
+  <si>
+    <t>Modal closes. Basket cleared. POS ready.</t>
+  </si>
+  <si>
+    <t>TC-079</t>
+  </si>
+  <si>
+    <t>9. Receipt Printing</t>
   </si>
   <si>
     <t>Print account receipt PDF</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete account payment
-2. Click Print Receipt in modal</t>
-  </si>
-  <si>
-    <t>PDF fetched via print-receipt endpoint. Opens in new tab. PDF size &gt; 5KB.</t>
-  </si>
-  <si>
-    <t>TC-078</t>
-  </si>
-  <si>
-    <t>Print misc receipt PDF (dedicated endpoint)</t>
+2. Print</t>
+  </si>
+  <si>
+    <t>PDF via print-receipt endpoint. Opens new tab. &gt;5KB.</t>
+  </si>
+  <si>
+    <t>TC-080</t>
+  </si>
+  <si>
+    <t>Print misc receipt (dedicated endpoint)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete misc payment
-2. Click Print Receipt in modal</t>
-  </si>
-  <si>
-    <t>PDF fetched via print-miscellaneous-receipt?id={receiptId} endpoint. PDF includes payer details, SCOA item, description.</t>
-  </si>
-  <si>
-    <t>TC-079</t>
-  </si>
-  <si>
-    <t>Print multi-account receipt PDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete multi-account payment
-2. Click Print Receipt</t>
-  </si>
-  <si>
-    <t>All receipt IDs sent in single print-receipt call. Combined PDF generated.</t>
-  </si>
-  <si>
-    <t>TC-080</t>
-  </si>
-  <si>
-    <t>Auto-print on payment success</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enable auto-print (if configured)
-2. Complete payment</t>
-  </si>
-  <si>
-    <t>Receipt automatically opens for printing after successful payment.</t>
+2. Print</t>
+  </si>
+  <si>
+    <t>PDF via print-miscellaneous-receipt?id={id}. Includes payer, SCOA, description.</t>
   </si>
   <si>
     <t>TC-081</t>
   </si>
   <si>
+    <t>Print multi-account receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete multi-account
+2. Print</t>
+  </si>
+  <si>
+    <t>Combined PDF with all receipt IDs.</t>
+  </si>
+  <si>
+    <t>TC-082</t>
+  </si>
+  <si>
     <t>Receipt PDF content verification</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Print receipt PDF
-2. Verify PDF contains receipt number matching API response</t>
-  </si>
-  <si>
-    <t>PDF content matches receipt number from reconcile list. PDF &gt; 5KB, valid PDF header.</t>
-  </si>
-  <si>
-    <t>TC-082</t>
-  </si>
-  <si>
-    <t>9. Receipt Search</t>
-  </si>
-  <si>
-    <t>Search receipts by date range</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to receipt search
-2. Enter date range
-3. Search</t>
-  </si>
-  <si>
-    <t>Returns receipts within date range with receipt numbers, amounts, dates in dd/mm/yyyy format.</t>
+    <t xml:space="preserve">1. Print PDF
+2. Verify receipt number</t>
+  </si>
+  <si>
+    <t>PDF content matches API receipt number. Valid PDF header.</t>
   </si>
   <si>
     <t>TC-083</t>
   </si>
   <si>
-    <t>Search receipts by receipt number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter specific receipt number
-2. Search</t>
-  </si>
-  <si>
-    <t>Returns matching receipt with full details.</t>
+    <t>10. Day-End Reconciliation</t>
+  </si>
+  <si>
+    <t>Navigate to Day-End page</t>
+  </si>
+  <si>
+    <t>1. Click "Day End" in POS header</t>
+  </si>
+  <si>
+    <t>Cashier Day End Reconcile page loads. Shows active session info.</t>
   </si>
   <si>
     <t>TC-084</t>
   </si>
   <si>
-    <t>Receipt detail view</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Find a receipt in search
-2. Click to view details</t>
-  </si>
-  <si>
-    <t>Shows full receipt details including payment type, amount, cashier, date.</t>
+    <t>Session info display</t>
+  </si>
+  <si>
+    <t>1. View session card on Day-End page</t>
+  </si>
+  <si>
+    <t>Shows Cashier Name, Cash Office, Reconcile Date (dd/mm/yyyy), Opening Float.</t>
   </si>
   <si>
     <t>TC-085</t>
   </si>
   <si>
-    <t>10. Day-End Reconciliation</t>
-  </si>
-  <si>
-    <t>View unreconciled list</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to Day End
-2. View unreconciled receipts</t>
-  </si>
-  <si>
-    <t>Lists all unreconciled receipts for current session with IDs, amounts, receipt numbers.</t>
+    <t>No active session state</t>
+  </si>
+  <si>
+    <t>1. Navigate to Day-End without session</t>
+  </si>
+  <si>
+    <t>"No Active Session" message. Cannot submit.</t>
   </si>
   <si>
     <t>TC-086</t>
   </si>
   <si>
-    <t>Verify account receipt in reconcile list</t>
+    <t>Daily Takings tab — Credit card receipts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. View Daily Takings tab
+2. Check Credit Card Receipts table</t>
+  </si>
+  <si>
+    <t>Shows all card receipts: Account/Invoice, Receipt No, Date, Cancelled status, Card No, Expiry, Amount. Total at bottom.</t>
+  </si>
+  <si>
+    <t>TC-087</t>
+  </si>
+  <si>
+    <t>Daily Takings tab — Reconcile list</t>
+  </si>
+  <si>
+    <t>1. View reconcile receipt list</t>
+  </si>
+  <si>
+    <t>All unreconciled receipts listed with IDs, amounts, receipt numbers.</t>
+  </si>
+  <si>
+    <t>TC-088</t>
+  </si>
+  <si>
+    <t>Denomination counting (notes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Toggle "Count by denomination" ON
+2. Enter note counts (R200, R100, R50, R20, R10)</t>
+  </si>
+  <si>
+    <t>Each denomination row accepts count. Running total for Notes section calculated.</t>
+  </si>
+  <si>
+    <t>TC-089</t>
+  </si>
+  <si>
+    <t>Denomination counting (coins)</t>
+  </si>
+  <si>
+    <t>1. Enter coin counts (R5, R2, R1, 50c, 20c, 10c, 5c, 1c)</t>
+  </si>
+  <si>
+    <t>Coin totals calculated correctly. Overall cash total = Notes + Coins.</t>
+  </si>
+  <si>
+    <t>TC-090</t>
+  </si>
+  <si>
+    <t>Manual cash total entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Toggle denomination counting OFF
+2. Enter manual cash total</t>
+  </si>
+  <si>
+    <t>Cash total accepted as manual entry instead of denomination count.</t>
+  </si>
+  <si>
+    <t>TC-091</t>
+  </si>
+  <si>
+    <t>Cash on hand + drop box total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter cash
+2. View combined total</t>
+  </si>
+  <si>
+    <t>Cash On Hand + Drop Box total displayed correctly.</t>
+  </si>
+  <si>
+    <t>TC-092</t>
+  </si>
+  <si>
+    <t>Grand total calculation</t>
+  </si>
+  <si>
+    <t>1. Cash + Card + Cheque totals entered</t>
+  </si>
+  <si>
+    <t>Grand Total = Cash on Hand + Drop Box + Credit Card total.</t>
+  </si>
+  <si>
+    <t>TC-093</t>
+  </si>
+  <si>
+    <t>Submit day-end reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Complete all counts
+2. Click Submit
+3. Confirm</t>
+  </si>
+  <si>
+    <t>3-step process: save-reconcile-data → validate-cashbook → submit-day-auth-reconcile. Success message: "Submitted for supervisor approval."</t>
+  </si>
+  <si>
+    <t>TC-094</t>
+  </si>
+  <si>
+    <t>Submit redirects to home</t>
+  </si>
+  <si>
+    <t>1. After successful submit</t>
+  </si>
+  <si>
+    <t>Redirected to home page after 1.5 seconds.</t>
+  </si>
+  <si>
+    <t>TC-095</t>
+  </si>
+  <si>
+    <t>Verify receipt in reconcile list (account)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete account payment
 2. Check reconcile list</t>
   </si>
   <si>
-    <t>Payment appears in reconcile list with matching receipt ID, amount, and receipt number.</t>
-  </si>
-  <si>
-    <t>TC-087</t>
-  </si>
-  <si>
-    <t>Verify misc receipt in reconcile list</t>
+    <t>Payment appears with matching receipt ID and amount.</t>
+  </si>
+  <si>
+    <t>TC-096</t>
+  </si>
+  <si>
+    <t>Verify receipt in reconcile list (misc)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete misc payment
 2. Check reconcile list</t>
   </si>
   <si>
-    <t>Misc payment appears in reconcile list with correct amount and receipt info.</t>
-  </si>
-  <si>
-    <t>TC-088</t>
-  </si>
-  <si>
-    <t>Verify multi-account receipt in reconcile list</t>
+    <t>Misc payment appears with correct amount.</t>
+  </si>
+  <si>
+    <t>TC-097</t>
+  </si>
+  <si>
+    <t>Verify receipt in reconcile list (multi-account)</t>
   </si>
   <si>
     <t xml:space="preserve">1. Complete multi-account payment
-2. Check reconcile list</t>
-  </si>
-  <si>
-    <t>Each account's receipt appears separately in the reconcile list.</t>
-  </si>
-  <si>
-    <t>TC-089</t>
-  </si>
-  <si>
-    <t>Day-end cash count entry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to Day End
-2. Enter denomination counts</t>
-  </si>
-  <si>
-    <t>Cash count form accepts denomination quantities. Running total calculates.</t>
-  </si>
-  <si>
-    <t>TC-090</t>
-  </si>
-  <si>
-    <t>Day-end variance calculation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Enter cash counts
-2. System compares to expected</t>
-  </si>
-  <si>
-    <t>Variance (surplus/shortfall) calculated and displayed. Over/short highlighted.</t>
-  </si>
-  <si>
-    <t>TC-091</t>
-  </si>
-  <si>
-    <t>Submit day-end reconciliation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete cash counts
+2. Check list</t>
+  </si>
+  <si>
+    <t>Each account receipt appears separately.</t>
+  </si>
+  <si>
+    <t>TC-098</t>
+  </si>
+  <si>
+    <t>11. Drop Box</t>
+  </si>
+  <si>
+    <t>Drop Box tab on Day-End</t>
+  </si>
+  <si>
+    <t>1. Click "Drop Box" tab on Day-End page</t>
+  </si>
+  <si>
+    <t>Drop Box tab shows count badge. Lists all drop box entries.</t>
+  </si>
+  <si>
+    <t>TC-099</t>
+  </si>
+  <si>
+    <t>Drop Box total</t>
+  </si>
+  <si>
+    <t>1. View drop box entries</t>
+  </si>
+  <si>
+    <t>Total amount calculated from all drop box items.</t>
+  </si>
+  <si>
+    <t>TC-100</t>
+  </si>
+  <si>
+    <t>Drop Box from POS header</t>
+  </si>
+  <si>
+    <t>1. Click "Drop Box" button in POS header</t>
+  </si>
+  <si>
+    <t>Cash drop box dialog opens. Session active required.</t>
+  </si>
+  <si>
+    <t>TC-101</t>
+  </si>
+  <si>
+    <t>Drop Box included in reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Have drop box entries
 2. Submit day-end</t>
   </si>
   <si>
-    <t>Day-end submitted for supervisor approval. Session status changes to "pending_approval".</t>
-  </si>
-  <si>
-    <t>TC-092</t>
-  </si>
-  <si>
-    <t>11. Header Actions</t>
-  </si>
-  <si>
-    <t>Enquiry button navigation</t>
-  </si>
-  <si>
-    <t>1. Click "Enquiry" button in header</t>
-  </si>
-  <si>
-    <t>Navigates to Account Enquiry page.</t>
-  </si>
-  <si>
-    <t>TC-093</t>
-  </si>
-  <si>
-    <t>Drop Box button</t>
-  </si>
-  <si>
-    <t>1. Click "Drop Box" button (session active required)</t>
-  </si>
-  <si>
-    <t>Cash drop box dialog opens.</t>
-  </si>
-  <si>
-    <t>TC-094</t>
+    <t>Drop box total included in Cash On Hand + Drop Box calculation.</t>
+  </si>
+  <si>
+    <t>TC-102</t>
+  </si>
+  <si>
+    <t>12. Receipt Cancellation</t>
+  </si>
+  <si>
+    <t>Request Cancellation tab</t>
+  </si>
+  <si>
+    <t>1. Click "Request Cancellation" tab on Day-End</t>
+  </si>
+  <si>
+    <t>Cancellation request form displayed with search field.</t>
+  </si>
+  <si>
+    <t>TC-103</t>
+  </si>
+  <si>
+    <t>Search receipt for cancellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter receipt number
+2. Click Search</t>
+  </si>
+  <si>
+    <t>Receipt found and displayed with details (receipt no, account, amount, date).</t>
+  </si>
+  <si>
+    <t>TC-104</t>
+  </si>
+  <si>
+    <t>Search receipt — not found</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter invalid receipt number
+2. Search</t>
+  </si>
+  <si>
+    <t>"No receipt found for [number]" error message.</t>
+  </si>
+  <si>
+    <t>TC-105</t>
+  </si>
+  <si>
+    <t>Submit cancellation request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search receipt successfully
+2. Enter cancellation reason
+3. Submit</t>
+  </si>
+  <si>
+    <t>Request submitted via request-cancel-receipt. Message: "Cancellation request submitted. Awaiting supervisor approval."</t>
+  </si>
+  <si>
+    <t>TC-106</t>
+  </si>
+  <si>
+    <t>Cancel without reason blocked</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Find receipt
+2. Leave reason blank
+3. Try submit</t>
+  </si>
+  <si>
+    <t>Error: "Please provide a reason for cancellation."</t>
+  </si>
+  <si>
+    <t>TC-107</t>
+  </si>
+  <si>
+    <t>Clear cancel search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. After search
+2. Click Clear</t>
+  </si>
+  <si>
+    <t>Search query, found receipt, and reason all cleared.</t>
+  </si>
+  <si>
+    <t>TC-108</t>
+  </si>
+  <si>
+    <t>Cancelled receipt indicator</t>
+  </si>
+  <si>
+    <t>1. View receipts in day-end lists</t>
+  </si>
+  <si>
+    <t>Cancelled receipts show red "Yes" badge in Cancelled column.</t>
+  </si>
+  <si>
+    <t>TC-109</t>
+  </si>
+  <si>
+    <t>Cancel request from POS header</t>
+  </si>
+  <si>
+    <t>1. Click "Cancel" button in POS header</t>
+  </si>
+  <si>
+    <t>Cancel receipt dialog opens. Session active required.</t>
+  </si>
+  <si>
+    <t>TC-110</t>
+  </si>
+  <si>
+    <t>13. Supervisor Dashboard</t>
+  </si>
+  <si>
+    <t>Dashboard loads</t>
+  </si>
+  <si>
+    <t>1. Navigate to Supervisor Dashboard</t>
+  </si>
+  <si>
+    <t>Page title "Supervisor Dashboard". Two tabs: Day-End Reconciliation, Cancellation Requests.</t>
+  </si>
+  <si>
+    <t>TC-111</t>
+  </si>
+  <si>
+    <t>Stats cards display</t>
+  </si>
+  <si>
+    <t>1. View stats row</t>
+  </si>
+  <si>
+    <t>Shows: Pending Approval count, With Variance count, Total Posted, System Revenue.</t>
+  </si>
+  <si>
+    <t>TC-112</t>
+  </si>
+  <si>
+    <t>Per Cashier mode</t>
+  </si>
+  <si>
+    <t>1. Select "Per Cashier" mode</t>
+  </si>
+  <si>
+    <t>Table shows all cashier shifts: Name, Office, Status, System Total, Declared, Variance, Receipts, Actions.</t>
+  </si>
+  <si>
+    <t>TC-113</t>
+  </si>
+  <si>
+    <t>Cash Office mode</t>
+  </si>
+  <si>
+    <t>1. Select "Cash Office" mode</t>
+  </si>
+  <si>
+    <t>Grid of cash office cards. Click to manage office-level reconciliation.</t>
+  </si>
+  <si>
+    <t>TC-114</t>
+  </si>
+  <si>
+    <t>Filter by office</t>
+  </si>
+  <si>
+    <t>1. Select office from dropdown filter</t>
+  </si>
+  <si>
+    <t>Cashier list filtered to selected office only.</t>
+  </si>
+  <si>
+    <t>TC-115</t>
+  </si>
+  <si>
+    <t>Filter by status</t>
+  </si>
+  <si>
+    <t>1. Select "Pending Approval" status filter</t>
+  </si>
+  <si>
+    <t>Only pending approval shifts shown.</t>
+  </si>
+  <si>
+    <t>TC-116</t>
+  </si>
+  <si>
+    <t>Search cashier by name</t>
+  </si>
+  <si>
+    <t>1. Type cashier name in search</t>
+  </si>
+  <si>
+    <t>List filtered to matching cashier names.</t>
+  </si>
+  <si>
+    <t>TC-117</t>
+  </si>
+  <si>
+    <t>Refresh button</t>
+  </si>
+  <si>
+    <t>1. Click Refresh button</t>
+  </si>
+  <si>
+    <t>Cashier list and cancellation requests reloaded.</t>
+  </si>
+  <si>
+    <t>TC-118</t>
+  </si>
+  <si>
+    <t>Status badges display</t>
+  </si>
+  <si>
+    <t>1. View shifts with different statuses</t>
+  </si>
+  <si>
+    <t>Pending=yellow/warning, Completed=green/success, Returned=red/danger, Not Submitted=grey.</t>
+  </si>
+  <si>
+    <t>TC-119</t>
+  </si>
+  <si>
+    <t>14. Supervisor Review</t>
+  </si>
+  <si>
+    <t>Review button on pending shift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Find pending shift
+2. Click "Review"</t>
+  </si>
+  <si>
+    <t>Review modal opens with cashier details.</t>
+  </si>
+  <si>
+    <t>TC-120</t>
+  </si>
+  <si>
+    <t>Review summary — system vs declared</t>
+  </si>
+  <si>
+    <t>1. View review summary</t>
+  </si>
+  <si>
+    <t>Shows System Total, Declared Total, and Variance.</t>
+  </si>
+  <si>
+    <t>TC-121</t>
+  </si>
+  <si>
+    <t>Cash Receipts tab</t>
+  </si>
+  <si>
+    <t>1. Click "Cash Receipts" tab in review</t>
+  </si>
+  <si>
+    <t>Lists all cash receipts: Receipt No, Account, Amount, Date, Cancel button.</t>
+  </si>
+  <si>
+    <t>TC-122</t>
+  </si>
+  <si>
+    <t>Card Receipts tab</t>
+  </si>
+  <si>
+    <t>1. Click "Card Receipts" tab</t>
+  </si>
+  <si>
+    <t>Lists all card receipts: Receipt No, Account, Amount, Date.</t>
+  </si>
+  <si>
+    <t>TC-123</t>
+  </si>
+  <si>
+    <t>System vs Cashier tab</t>
+  </si>
+  <si>
+    <t>1. Click "System vs Cashier" tab</t>
+  </si>
+  <si>
+    <t>Comparison table: Description, System Amount, Cashier Amount, Variance (colour-coded +/-).</t>
+  </si>
+  <si>
+    <t>TC-124</t>
+  </si>
+  <si>
+    <t>Variance — surplus (positive)</t>
+  </si>
+  <si>
+    <t>1. Cashier declares more than system</t>
+  </si>
+  <si>
+    <t>Positive variance shown. Surplus highlighted in green.</t>
+  </si>
+  <si>
+    <t>TC-125</t>
+  </si>
+  <si>
+    <t>Variance — shortage (negative)</t>
+  </si>
+  <si>
+    <t>1. Cashier declares less than system</t>
+  </si>
+  <si>
+    <t>Negative variance shown. Shortage highlighted in red.</t>
+  </si>
+  <si>
+    <t>TC-126</t>
+  </si>
+  <si>
+    <t>Approve day-end reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Review shift
+2. Click "Approve"</t>
+  </si>
+  <si>
+    <t>Calls validate-cashbook → submit-day-auth-reconcile → finish-day-end-reconcile. Success: "Approved successfully." Status → Completed.</t>
+  </si>
+  <si>
+    <t>TC-127</t>
+  </si>
+  <si>
+    <t>Return day-end to cashier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Review shift
+2. Enter return reason
+3. Click "Return"</t>
+  </si>
+  <si>
+    <t>Calls return-day-end-reconcile with reason. Success: "Returned to cashier." Status → Returned.</t>
+  </si>
+  <si>
+    <t>TC-128</t>
+  </si>
+  <si>
+    <t>Return without reason blocked</t>
+  </si>
+  <si>
+    <t>1. Try to return without entering reason</t>
+  </si>
+  <si>
+    <t>"Return" button disabled until reason entered.</t>
+  </si>
+  <si>
+    <t>TC-129</t>
+  </si>
+  <si>
+    <t>Print Cash Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. In review modal
+2. Click "Print Cash Report"</t>
+  </si>
+  <si>
+    <t>PDF generated via print-cash-report. Opens in new tab.</t>
+  </si>
+  <si>
+    <t>TC-130</t>
+  </si>
+  <si>
+    <t>Print Deposit Slip</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. In review modal
+2. Click "Print Deposit Slip"</t>
+  </si>
+  <si>
+    <t>PDF generated via print-deposit-slip. Opens in new tab.</t>
+  </si>
+  <si>
+    <t>TC-131</t>
+  </si>
+  <si>
+    <t>Direct cancel receipt (supervisor)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. In review Cash Receipts tab
+2. Click "Cancel Receipt" on a receipt
+3. Enter reason
+4. Confirm</t>
+  </si>
+  <si>
+    <t>Receipt directly cancelled via cancel-receipt. "Voided" badge appears. Inline cancel form with reason field.</t>
+  </si>
+  <si>
+    <t>TC-132</t>
+  </si>
+  <si>
+    <t>Close review modal</t>
+  </si>
+  <si>
+    <t>1. Click X on review modal</t>
+  </si>
+  <si>
+    <t>Modal closes. Returns to cashier list.</t>
+  </si>
+  <si>
+    <t>TC-133</t>
+  </si>
+  <si>
+    <t>15. Cancellation Requests</t>
+  </si>
+  <si>
+    <t>Cancellations tab</t>
+  </si>
+  <si>
+    <t>1. Click "Cancellation Requests" tab</t>
+  </si>
+  <si>
+    <t>Shows pending requests with badge count. Table: Receipt No, Account, Amount, Cashier, Reason, Date, Actions.</t>
+  </si>
+  <si>
+    <t>TC-134</t>
+  </si>
+  <si>
+    <t>Approve cancellation request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Find pending request
+2. Click "Approve"</t>
+  </si>
+  <si>
+    <t>Receipt voided via approve-cancel-receipt. Success message. Request removed from list.</t>
+  </si>
+  <si>
+    <t>TC-135</t>
+  </si>
+  <si>
+    <t>Decline cancellation request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Find pending request
+2. Click "Decline"</t>
+  </si>
+  <si>
+    <t>Request declined via decline-cancel-receipt. Success message. Request removed from list.</t>
+  </si>
+  <si>
+    <t>TC-136</t>
+  </si>
+  <si>
+    <t>No pending requests state</t>
+  </si>
+  <si>
+    <t>1. All requests processed</t>
+  </si>
+  <si>
+    <t>"No pending cancellation requests" message.</t>
+  </si>
+  <si>
+    <t>TC-137</t>
+  </si>
+  <si>
+    <t>Misc receipt cancellation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Cancel request for misc receipt
+2. Approve</t>
+  </si>
+  <si>
+    <t>isMiscPayment flag sent correctly. Misc receipt voided.</t>
+  </si>
+  <si>
+    <t>TC-138</t>
+  </si>
+  <si>
+    <t>16. Per-Office Reconciliation</t>
+  </si>
+  <si>
+    <t>Cash Office selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Cash Office mode
+2. Click on an office card</t>
+  </si>
+  <si>
+    <t>Office details loaded: cashier summary with names, statuses, totals.</t>
+  </si>
+  <si>
+    <t>TC-139</t>
+  </si>
+  <si>
+    <t>Verify individual cashier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. In office view
+2. Click "Verify" for a cashier</t>
+  </si>
+  <si>
+    <t>Cashier reconcile verified via verify-cashier-reconcile endpoint.</t>
+  </si>
+  <si>
+    <t>TC-140</t>
+  </si>
+  <si>
+    <t>Check cashier status</t>
+  </si>
+  <si>
+    <t>1. Click "Status" for a cashier</t>
+  </si>
+  <si>
+    <t>Current reconcile status loaded and displayed.</t>
+  </si>
+  <si>
+    <t>TC-141</t>
+  </si>
+  <si>
+    <t>Submit per-office reconciliation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. All cashiers verified
+2. Submit office reconcile</t>
+  </si>
+  <si>
+    <t>Office-level reconciliation submitted via submit-reconcile-per-office.</t>
+  </si>
+  <si>
+    <t>TC-142</t>
+  </si>
+  <si>
+    <t>17. View Receipts</t>
+  </si>
+  <si>
+    <t>Receipt search by date range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to View Receipts
+2. Set from/to dates
+3. Search</t>
+  </si>
+  <si>
+    <t>Returns receipts within date range. Dates in dd/mm/yyyy.</t>
+  </si>
+  <si>
+    <t>TC-143</t>
+  </si>
+  <si>
+    <t>Receipt search by cashier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Select cashier from dropdown
+2. Search</t>
+  </si>
+  <si>
+    <t>Filtered to selected cashier's receipts only.</t>
+  </si>
+  <si>
+    <t>TC-144</t>
+  </si>
+  <si>
+    <t>Receipt search by account number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter account number
+2. Search</t>
+  </si>
+  <si>
+    <t>Returns receipts for that account.</t>
+  </si>
+  <si>
+    <t>TC-145</t>
+  </si>
+  <si>
+    <t>Receipt search by receipt number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Enter receipt number
+2. Search</t>
+  </si>
+  <si>
+    <t>Returns matching receipt with full details.</t>
+  </si>
+  <si>
+    <t>TC-146</t>
+  </si>
+  <si>
+    <t>Filter by payment method</t>
+  </si>
+  <si>
+    <t>1. Select "Cash" or "Credit Card" filter</t>
+  </si>
+  <si>
+    <t>Results filtered to selected payment method only.</t>
+  </si>
+  <si>
+    <t>TC-147</t>
+  </si>
+  <si>
+    <t>Filter by payment option</t>
+  </si>
+  <si>
+    <t>1. Select payment option filter</t>
+  </si>
+  <si>
+    <t>Results filtered to selected option (Consumer, Miscellaneous, etc.).</t>
+  </si>
+  <si>
+    <t>TC-148</t>
+  </si>
+  <si>
+    <t>Filter by status (active/cancelled)</t>
+  </si>
+  <si>
+    <t>1. Select "Active" or "Cancelled" status filter</t>
+  </si>
+  <si>
+    <t>Shows only active or cancelled receipts respectively.</t>
+  </si>
+  <si>
+    <t>TC-149</t>
+  </si>
+  <si>
+    <t>Quick search</t>
+  </si>
+  <si>
+    <t>1. Type in quick search field</t>
+  </si>
+  <si>
+    <t>Real-time filtering by account, receipt no, cashier name.</t>
+  </si>
+  <si>
+    <t>TC-150</t>
+  </si>
+  <si>
+    <t>Sort receipts</t>
+  </si>
+  <si>
+    <t>1. Click column headers to sort</t>
+  </si>
+  <si>
+    <t>Sorts by receipt no, account, amount, date (asc/desc toggle).</t>
+  </si>
+  <si>
+    <t>TC-151</t>
+  </si>
+  <si>
+    <t>Print individual receipt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Find receipt
+2. Click print button</t>
+  </si>
+  <si>
+    <t>Receipt PDF generated and opened.</t>
+  </si>
+  <si>
+    <t>TC-152</t>
+  </si>
+  <si>
+    <t>View receipt detail</t>
+  </si>
+  <si>
+    <t>1. Click on receipt row</t>
+  </si>
+  <si>
+    <t>Detail view showing payment type, option, cashier, office, amount, cancellation status.</t>
+  </si>
+  <si>
+    <t>TC-153</t>
+  </si>
+  <si>
+    <t>Bank Statement Trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Switch to Bank Statement tab
+2. Enter search text</t>
+  </si>
+  <si>
+    <t>Searches by bank statement notes. Returns matches with amounts, dates, allocation status.</t>
+  </si>
+  <si>
+    <t>TC-154</t>
+  </si>
+  <si>
+    <t>EFT Account Trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Switch to EFT Account tab
+2. Enter account number</t>
+  </si>
+  <si>
+    <t>Returns EFT bank statement notes for account.</t>
+  </si>
+  <si>
+    <t>TC-155</t>
+  </si>
+  <si>
+    <t>Cashbook Trace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Switch to Cashbook Trace tab
+2. Enter bank reference</t>
+  </si>
+  <si>
+    <t>Traces transaction through cashbook system.</t>
+  </si>
+  <si>
+    <t>TC-156</t>
+  </si>
+  <si>
+    <t>EFT Description search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Switch to EFT Description tab
+2. Enter description</t>
+  </si>
+  <si>
+    <t>Searches EFT transactions by description.</t>
+  </si>
+  <si>
+    <t>TC-157</t>
+  </si>
+  <si>
+    <t>Pagination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Search returns &gt; 50 results
+2. Navigate pages</t>
+  </si>
+  <si>
+    <t>Pagination controls work. 50 per page.</t>
+  </si>
+  <si>
+    <t>TC-158</t>
+  </si>
+  <si>
+    <t>Cancelled receipt display</t>
+  </si>
+  <si>
+    <t>1. View cancelled receipt in list</t>
+  </si>
+  <si>
+    <t>Cancelled receipts marked with cancellation indicator and reason.</t>
+  </si>
+  <si>
+    <t>TC-159</t>
+  </si>
+  <si>
+    <t>18. Header Actions</t>
+  </si>
+  <si>
+    <t>Enquiry button</t>
+  </si>
+  <si>
+    <t>1. Click "Enquiry" in header</t>
+  </si>
+  <si>
+    <t>Navigates to Account Enquiry.</t>
+  </si>
+  <si>
+    <t>TC-160</t>
+  </si>
+  <si>
+    <t>Day End button</t>
+  </si>
+  <si>
+    <t>1. Click "Day End" in header</t>
+  </si>
+  <si>
+    <t>Navigates to Day-End Reconciliation.</t>
+  </si>
+  <si>
+    <t>TC-161</t>
+  </si>
+  <si>
+    <t>Setup button</t>
+  </si>
+  <si>
+    <t>1. Click "Setup" in header</t>
+  </si>
+  <si>
+    <t>Navigates to Cashier Setup.</t>
+  </si>
+  <si>
+    <t>TC-162</t>
   </si>
   <si>
     <t>CSV Import button</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Click "Import" button
-2. Select CSV/Excel file</t>
-  </si>
-  <si>
-    <t>CSV import dialog opens. Accepts file upload for bulk payment processing.</t>
-  </si>
-  <si>
-    <t>TC-095</t>
-  </si>
-  <si>
-    <t>Cancel Receipt button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Click "Cancel" button
-2. Enter receipt details</t>
-  </si>
-  <si>
-    <t>Cancel receipt dialog opens. Submits cancellation request to supervisor.</t>
-  </si>
-  <si>
-    <t>TC-096</t>
-  </si>
-  <si>
-    <t>Day End button navigation</t>
-  </si>
-  <si>
-    <t>1. Click "Day End" button in header</t>
-  </si>
-  <si>
-    <t>Navigates to Day-End Reconciliation page.</t>
-  </si>
-  <si>
-    <t>TC-097</t>
-  </si>
-  <si>
-    <t>Setup button navigation</t>
-  </si>
-  <si>
-    <t>1. Click "Setup" button in header</t>
-  </si>
-  <si>
-    <t>Navigates to Cashier Setup page.</t>
-  </si>
-  <si>
-    <t>TC-098</t>
-  </si>
-  <si>
-    <t>Header buttons disabled without session</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Before cashier setup
-2. Check Drop Box, Import, Cancel buttons</t>
-  </si>
-  <si>
-    <t>Buttons disabled when no active cashier session.</t>
-  </si>
-  <si>
-    <t>TC-099</t>
-  </si>
-  <si>
-    <t>12. Business Rules</t>
-  </si>
-  <si>
-    <t>Only cash, card, cash+card tender types</t>
-  </si>
-  <si>
-    <t>1. View available tender tabs in payment panel</t>
-  </si>
-  <si>
-    <t>Only Cash, Card, and Cash+Card tender types available. EFT and Cheque permanently removed.</t>
-  </si>
-  <si>
-    <t>TC-100</t>
-  </si>
-  <si>
-    <t>Cash rounding — nearest 10c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Total = R15.03 → rounds to R15.00
-2. Total = R15.05 → rounds to R15.10
-3. Total = R15.08 → rounds to R15.10</t>
-  </si>
-  <si>
-    <t>SA 10c rounding applied correctly. Rounding indicator shown in UI.</t>
-  </si>
-  <si>
-    <t>TC-101</t>
-  </si>
-  <si>
-    <t>Change capped at R200</t>
-  </si>
-  <si>
-    <t>1. Overpay by more than R200 in cash</t>
-  </si>
-  <si>
-    <t>Error: "Change cannot exceed R200". Submit blocked.</t>
-  </si>
-  <si>
-    <t>TC-102</t>
-  </si>
-  <si>
-    <t>Zero amount blocked</t>
-  </si>
-  <si>
-    <t>1. Set pay amount to R0 for any item</t>
-  </si>
-  <si>
-    <t>TC-103</t>
-  </si>
-  <si>
-    <t>Card payment — zero change</t>
-  </si>
-  <si>
-    <t>1. Pay by card with overpayment</t>
-  </si>
-  <si>
-    <t>No cash change for card payments. Card overpay shown as warning.</t>
-  </si>
-  <si>
-    <t>TC-104</t>
-  </si>
-  <si>
-    <t>Receipt number resolution order</t>
-  </si>
-  <si>
-    <t>1. After payment, verify receipt number resolution</t>
-  </si>
-  <si>
-    <t>Resolution order: 1) Direct receiptNo from response, 2) Unreconciled list lookup, 3) pos-multi-receipt-print fallback, 4) REC-{id} last resort.</t>
-  </si>
-  <si>
-    <t>TC-105</t>
-  </si>
-  <si>
-    <t>13. Date &amp; Display Format</t>
-  </si>
-  <si>
-    <t>All dates in dd/mm/yyyy format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Check receipt dates, transaction dates, reconcile dates
-2. Verify format across all screens</t>
-  </si>
-  <si>
-    <t>ALL dates displayed as dd/mm/yyyy using padStart(2,"0") pattern. No "short month" or "medium" format anywhere.</t>
-  </si>
-  <si>
-    <t>TC-106</t>
+    <t xml:space="preserve">1. Click "Import"
+2. Upload CSV</t>
+  </si>
+  <si>
+    <t>CSV import dialog. Accounts validated and added to basket.</t>
+  </si>
+  <si>
+    <t>TC-163</t>
+  </si>
+  <si>
+    <t>Buttons disabled without session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. No active session
+2. Check Drop Box, Import, Cancel</t>
+  </si>
+  <si>
+    <t>All disabled when no session.</t>
+  </si>
+  <si>
+    <t>TC-164</t>
+  </si>
+  <si>
+    <t>19. Business Rules</t>
+  </si>
+  <si>
+    <t>Only cash, card, cash+card tenders</t>
+  </si>
+  <si>
+    <t>1. View tender tabs</t>
+  </si>
+  <si>
+    <t>Only Cash, Card, Cash+Card. EFT/Cheque permanently removed.</t>
+  </si>
+  <si>
+    <t>TC-165</t>
+  </si>
+  <si>
+    <t>Cash rounding (10c)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. R15.03→R15.00
+2. R15.05→R15.10
+3. R15.08→R15.10</t>
+  </si>
+  <si>
+    <t>SA 10c rounding correct. Indicator shown.</t>
+  </si>
+  <si>
+    <t>TC-166</t>
+  </si>
+  <si>
+    <t>Change capped R200</t>
+  </si>
+  <si>
+    <t>1. Overpay &gt; R200 in cash</t>
+  </si>
+  <si>
+    <t>Blocked with error message.</t>
+  </si>
+  <si>
+    <t>TC-167</t>
+  </si>
+  <si>
+    <t>1. Set pay to R0</t>
+  </si>
+  <si>
+    <t>Submit disabled.</t>
+  </si>
+  <si>
+    <t>TC-168</t>
+  </si>
+  <si>
+    <t>Card — zero change</t>
+  </si>
+  <si>
+    <t>No cash change. Overpay warning.</t>
+  </si>
+  <si>
+    <t>TC-169</t>
+  </si>
+  <si>
+    <t>Receipt number resolution</t>
+  </si>
+  <si>
+    <t>1. After payment, verify resolution</t>
+  </si>
+  <si>
+    <t>1) Direct receiptNo, 2) Unreconciled list, 3) pos-multi-receipt-print, 4) REC-{id} last resort.</t>
+  </si>
+  <si>
+    <t>TC-170</t>
+  </si>
+  <si>
+    <t>20. Date &amp; Display</t>
+  </si>
+  <si>
+    <t>All dates dd/mm/yyyy</t>
+  </si>
+  <si>
+    <t>1. Check dates everywhere</t>
+  </si>
+  <si>
+    <t>ALL dates dd/mm/yyyy with padStart(2,"0"). Never short month format.</t>
+  </si>
+  <si>
+    <t>TC-171</t>
   </si>
   <si>
     <t>Currency formatting</t>
   </si>
   <si>
-    <t>1. Check amounts across POS, basket, summary, receipt modal</t>
-  </si>
-  <si>
-    <t>All amounts formatted as "R x,xxx.xx" with proper decimal places.</t>
-  </si>
-  <si>
-    <t>TC-107</t>
-  </si>
-  <si>
-    <t>Receipt number monospace display</t>
-  </si>
-  <si>
-    <t>1. View receipt numbers in receipt modal</t>
-  </si>
-  <si>
-    <t>Receipt numbers shown in monospace font for clarity.</t>
-  </si>
-  <si>
-    <t>TC-108</t>
-  </si>
-  <si>
-    <t>14. UI Theme &amp; Layout</t>
-  </si>
-  <si>
-    <t>Platinum theme colours</t>
-  </si>
-  <si>
-    <t>1. Inspect POS header and buttons</t>
-  </si>
-  <si>
-    <t>Navy primary (#0f2b46), Gold accent (#c9a84c), white surfaces, Inter font. Light theme throughout.</t>
-  </si>
-  <si>
-    <t>TC-109</t>
-  </si>
-  <si>
-    <t>Dynamic vs Tab search modes</t>
-  </si>
-  <si>
-    <t>1. Toggle between "Dynamic Search" and "Category Tabs"</t>
-  </si>
-  <si>
-    <t>Toggle switches correctly. Dynamic shows unified search box. Tabs show Account/Clearance/Prepaid/Misc tabs.</t>
-  </si>
-  <si>
-    <t>TC-110</t>
-  </si>
-  <si>
-    <t>Responsive layout — split panel</t>
-  </si>
-  <si>
-    <t>1. View POS in standard resolution</t>
-  </si>
-  <si>
-    <t>Left panel (search/basket) and right panel (payment summary) side by side.</t>
-  </si>
-  <si>
-    <t>TC-111</t>
-  </si>
-  <si>
-    <t>Type badge colours</t>
-  </si>
-  <si>
-    <t>1. Add items of all types to basket</t>
-  </si>
-  <si>
-    <t>Consumer=blue, Clearance=green, Prepaid=orange, Misc=purple. Consistent across basket and receipt modal.</t>
-  </si>
-  <si>
-    <t>TC-112</t>
-  </si>
-  <si>
-    <t>15. Error Handling</t>
-  </si>
-  <si>
-    <t>API timeout handling</t>
-  </si>
-  <si>
-    <t>1. Simulate slow API response (or test with large batch)</t>
-  </si>
-  <si>
-    <t>Loading spinner shown. Timeout handled gracefully with user-friendly error message.</t>
-  </si>
-  <si>
-    <t>TC-113</t>
-  </si>
-  <si>
-    <t>Payment failure handling</t>
-  </si>
-  <si>
-    <t>1. Submit payment that fails (e.g. invalid data)</t>
-  </si>
-  <si>
-    <t>Error message displayed in toast notification. Basket preserved for retry.</t>
-  </si>
-  <si>
-    <t>TC-114</t>
-  </si>
-  <si>
-    <t>Session expiry handling</t>
+    <t>1. Check amounts everywhere</t>
+  </si>
+  <si>
+    <t>R x,xxx.xx format.</t>
+  </si>
+  <si>
+    <t>TC-172</t>
+  </si>
+  <si>
+    <t>Platinum theme</t>
+  </si>
+  <si>
+    <t>1. Check colours</t>
+  </si>
+  <si>
+    <t>Navy #0f2b46, Gold #c9a84c, white surfaces, Inter font, light theme.</t>
+  </si>
+  <si>
+    <t>TC-173</t>
+  </si>
+  <si>
+    <t>21. Error Handling</t>
+  </si>
+  <si>
+    <t>API timeout</t>
+  </si>
+  <si>
+    <t>1. Slow response scenario</t>
+  </si>
+  <si>
+    <t>Loading spinner. Graceful timeout error.</t>
+  </si>
+  <si>
+    <t>TC-174</t>
+  </si>
+  <si>
+    <t>Payment failure</t>
+  </si>
+  <si>
+    <t>1. Submit invalid payment</t>
+  </si>
+  <si>
+    <t>Error toast. Basket preserved for retry.</t>
+  </si>
+  <si>
+    <t>TC-175</t>
+  </si>
+  <si>
+    <t>Session expiry</t>
   </si>
   <si>
     <t xml:space="preserve">1. Let session expire
-2. Try to perform action</t>
-  </si>
-  <si>
-    <t>Redirected to login or shown session expired message.</t>
-  </si>
-  <si>
-    <t>TC-115</t>
-  </si>
-  <si>
-    <t>Empty receipt PDF handling</t>
-  </si>
-  <si>
-    <t>1. Receipt PDF returns empty/blank</t>
-  </si>
-  <si>
-    <t>Error message: "Empty receipt PDF" shown. Not a blank window.</t>
-  </si>
-  <si>
-    <t>TC-116</t>
-  </si>
-  <si>
-    <t>16. Receipt Delivery</t>
-  </si>
-  <si>
-    <t>Send receipt section in modal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Complete payment
-2. View "Send Receipt" section in receipt modal</t>
-  </si>
-  <si>
-    <t>Send receipt options displayed (email, SMS if available).</t>
-  </si>
-  <si>
-    <t>TC-117</t>
-  </si>
-  <si>
-    <t>17. CSV Import</t>
-  </si>
-  <si>
-    <t>Open CSV import dialog</t>
-  </si>
-  <si>
-    <t>1. Click Import button in header</t>
-  </si>
-  <si>
-    <t>CSV import dialog opens with file upload area.</t>
-  </si>
-  <si>
-    <t>TC-118</t>
-  </si>
-  <si>
-    <t>Import valid CSV file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Upload CSV with valid account numbers and amounts
-2. Process import</t>
-  </si>
-  <si>
-    <t>Accounts validated and added to basket with correct amounts from CSV.</t>
-  </si>
-  <si>
-    <t>TC-119</t>
-  </si>
-  <si>
-    <t>Import CSV with invalid data</t>
-  </si>
-  <si>
-    <t>1. Upload CSV with invalid account numbers</t>
-  </si>
-  <si>
-    <t>Invalid rows flagged with error messages. Valid rows still importable.</t>
-  </si>
-  <si>
-    <t>TOTAL TEST CASES: 119 | Agent Pass: 119 | Agent Fail: 0</t>
+2. Try action</t>
+  </si>
+  <si>
+    <t>Redirect to login or session expired message.</t>
+  </si>
+  <si>
+    <t>TC-176</t>
+  </si>
+  <si>
+    <t>Empty receipt PDF</t>
+  </si>
+  <si>
+    <t>1. PDF returns blank</t>
+  </si>
+  <si>
+    <t>"Empty receipt PDF" error. Not blank window.</t>
+  </si>
+  <si>
+    <t>TC-177</t>
+  </si>
+  <si>
+    <t>Day-end submit failure</t>
+  </si>
+  <si>
+    <t>1. Day-end API returns error</t>
+  </si>
+  <si>
+    <t>Error message shown. Form preserved for retry.</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASES: 177 | Agent Pass: 177 | Agent Fail: 0</t>
   </si>
   <si>
     <t>GEORGE MUNICIPALITY — POS SYSTEM FEATURE REQUESTS</t>
@@ -2527,11 +3231,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O124"/>
+  <dimension ref="A1:O182"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="5" width="55" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -2926,17 +3630,17 @@
       <c r="A12" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="D12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>22</v>
@@ -2959,10 +3663,10 @@
     </row>
     <row r="13" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>59</v>
@@ -3766,17 +4470,17 @@
       <c r="A36" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>24</v>
+      <c r="B36" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F36" s="8" t="s">
         <v>22</v>
@@ -3799,19 +4503,19 @@
     </row>
     <row r="37" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>22</v>
@@ -3834,19 +4538,19 @@
     </row>
     <row r="38" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>22</v>
@@ -3869,19 +4573,19 @@
     </row>
     <row r="39" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F39" s="8" t="s">
         <v>22</v>
@@ -3904,10 +4608,10 @@
     </row>
     <row r="40" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" s="7" t="s">
         <v>168</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>169</v>
@@ -4081,17 +4785,17 @@
       <c r="A45" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="D45" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="E45" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="F45" s="8" t="s">
         <v>22</v>
@@ -4114,19 +4818,19 @@
     </row>
     <row r="46" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="E46" s="6" t="s">
         <v>195</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>196</v>
       </c>
       <c r="F46" s="8" t="s">
         <v>22</v>
@@ -4149,19 +4853,19 @@
     </row>
     <row r="47" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" s="6" t="s">
+      <c r="D47" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="E47" s="6" t="s">
         <v>199</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>200</v>
       </c>
       <c r="F47" s="8" t="s">
         <v>22</v>
@@ -4184,19 +4888,19 @@
     </row>
     <row r="48" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C48" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="E48" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="F48" s="8" t="s">
         <v>22</v>
@@ -4219,10 +4923,10 @@
     </row>
     <row r="49" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B49" s="7" t="s">
         <v>205</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>206</v>
@@ -4326,17 +5030,17 @@
       <c r="A52" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
+      <c r="B52" s="7" t="s">
+        <v>218</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>22</v>
@@ -4359,19 +5063,19 @@
     </row>
     <row r="53" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F53" s="8" t="s">
         <v>22</v>
@@ -4394,19 +5098,19 @@
     </row>
     <row r="54" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F54" s="8" t="s">
         <v>22</v>
@@ -4429,19 +5133,19 @@
     </row>
     <row r="55" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F55" s="8" t="s">
         <v>22</v>
@@ -4464,19 +5168,19 @@
     </row>
     <row r="56" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F56" s="8" t="s">
         <v>22</v>
@@ -4499,19 +5203,19 @@
     </row>
     <row r="57" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F57" s="8" t="s">
         <v>22</v>
@@ -4534,19 +5238,19 @@
     </row>
     <row r="58" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>22</v>
@@ -4569,19 +5273,19 @@
     </row>
     <row r="59" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F59" s="8" t="s">
         <v>22</v>
@@ -4604,19 +5308,19 @@
     </row>
     <row r="60" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F60" s="8" t="s">
         <v>22</v>
@@ -4639,10 +5343,10 @@
     </row>
     <row r="61" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B61" s="7" t="s">
         <v>254</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>255</v>
@@ -4781,17 +5485,17 @@
       <c r="A65" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>24</v>
+      <c r="B65" s="7" t="s">
+        <v>271</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F65" s="8" t="s">
         <v>22</v>
@@ -4814,19 +5518,19 @@
     </row>
     <row r="66" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>22</v>
@@ -4849,19 +5553,19 @@
     </row>
     <row r="67" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F67" s="8" t="s">
         <v>22</v>
@@ -4884,19 +5588,19 @@
     </row>
     <row r="68" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>22</v>
@@ -4919,19 +5623,19 @@
     </row>
     <row r="69" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F69" s="8" t="s">
         <v>22</v>
@@ -4954,10 +5658,10 @@
     </row>
     <row r="70" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="B70" s="7" t="s">
         <v>291</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>292</v>
@@ -5061,17 +5765,17 @@
       <c r="A73" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>24</v>
+      <c r="B73" s="7" t="s">
+        <v>304</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F73" s="8" t="s">
         <v>22</v>
@@ -5094,19 +5798,19 @@
     </row>
     <row r="74" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F74" s="8" t="s">
         <v>22</v>
@@ -5129,19 +5833,19 @@
     </row>
     <row r="75" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F75" s="8" t="s">
         <v>22</v>
@@ -5164,19 +5868,19 @@
     </row>
     <row r="76" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F76" s="8" t="s">
         <v>22</v>
@@ -5199,19 +5903,19 @@
     </row>
     <row r="77" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F77" s="8" t="s">
         <v>22</v>
@@ -5234,19 +5938,19 @@
     </row>
     <row r="78" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F78" s="8" t="s">
         <v>22</v>
@@ -5269,19 +5973,19 @@
     </row>
     <row r="79" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F79" s="8" t="s">
         <v>22</v>
@@ -5304,10 +6008,10 @@
     </row>
     <row r="80" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="B80" s="7" t="s">
         <v>332</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>333</v>
@@ -5376,17 +6080,17 @@
       <c r="A82" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="B82" s="6" t="s">
-        <v>24</v>
+      <c r="B82" s="7" t="s">
+        <v>341</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>22</v>
@@ -5409,19 +6113,19 @@
     </row>
     <row r="83" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F83" s="8" t="s">
         <v>22</v>
@@ -5444,19 +6148,19 @@
     </row>
     <row r="84" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F84" s="8" t="s">
         <v>22</v>
@@ -5479,10 +6183,10 @@
     </row>
     <row r="85" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="B85" s="7" t="s">
         <v>353</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>354</v>
@@ -5516,17 +6220,17 @@
       <c r="A86" s="6" t="s">
         <v>357</v>
       </c>
-      <c r="B86" s="6" t="s">
-        <v>24</v>
+      <c r="B86" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F86" s="8" t="s">
         <v>22</v>
@@ -5549,19 +6253,19 @@
     </row>
     <row r="87" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F87" s="8" t="s">
         <v>22</v>
@@ -5584,10 +6288,10 @@
     </row>
     <row r="88" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="B88" s="7" t="s">
         <v>366</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>367</v>
@@ -5831,17 +6535,17 @@
       <c r="A95" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C95" s="6" t="s">
         <v>395</v>
       </c>
-      <c r="C95" s="6" t="s">
+      <c r="D95" s="6" t="s">
         <v>396</v>
       </c>
-      <c r="D95" s="6" t="s">
+      <c r="E95" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="F95" s="8" t="s">
         <v>22</v>
@@ -5864,19 +6568,19 @@
     </row>
     <row r="96" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C96" s="6" t="s">
         <v>399</v>
       </c>
-      <c r="B96" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C96" s="6" t="s">
+      <c r="D96" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="D96" s="6" t="s">
+      <c r="E96" s="6" t="s">
         <v>401</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>402</v>
       </c>
       <c r="F96" s="8" t="s">
         <v>22</v>
@@ -5899,19 +6603,19 @@
     </row>
     <row r="97" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>403</v>
       </c>
-      <c r="B97" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C97" s="6" t="s">
+      <c r="D97" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="E97" s="6" t="s">
         <v>405</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>406</v>
       </c>
       <c r="F97" s="8" t="s">
         <v>22</v>
@@ -5934,19 +6638,19 @@
     </row>
     <row r="98" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="B98" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C98" s="6" t="s">
+      <c r="D98" s="6" t="s">
         <v>408</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="E98" s="6" t="s">
         <v>409</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>410</v>
       </c>
       <c r="F98" s="8" t="s">
         <v>22</v>
@@ -5969,19 +6673,19 @@
     </row>
     <row r="99" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="6" t="s">
         <v>411</v>
       </c>
-      <c r="B99" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C99" s="6" t="s">
+      <c r="D99" s="6" t="s">
         <v>412</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="E99" s="6" t="s">
         <v>413</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>414</v>
       </c>
       <c r="F99" s="8" t="s">
         <v>22</v>
@@ -6004,19 +6708,19 @@
     </row>
     <row r="100" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C100" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="B100" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C100" s="6" t="s">
+      <c r="D100" s="6" t="s">
         <v>416</v>
       </c>
-      <c r="D100" s="6" t="s">
+      <c r="E100" s="6" t="s">
         <v>417</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>418</v>
       </c>
       <c r="F100" s="8" t="s">
         <v>22</v>
@@ -6039,10 +6743,10 @@
     </row>
     <row r="101" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B101" s="7" t="s">
         <v>419</v>
-      </c>
-      <c r="B101" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>420</v>
@@ -6076,17 +6780,17 @@
       <c r="A102" s="6" t="s">
         <v>423</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>424</v>
       </c>
-      <c r="C102" s="6" t="s">
+      <c r="D102" s="6" t="s">
         <v>425</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="E102" s="6" t="s">
         <v>426</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>427</v>
       </c>
       <c r="F102" s="8" t="s">
         <v>22</v>
@@ -6109,19 +6813,19 @@
     </row>
     <row r="103" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C103" s="6" t="s">
         <v>428</v>
       </c>
-      <c r="B103" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C103" s="6" t="s">
+      <c r="D103" s="6" t="s">
         <v>429</v>
       </c>
-      <c r="D103" s="6" t="s">
+      <c r="E103" s="6" t="s">
         <v>430</v>
-      </c>
-      <c r="E103" s="6" t="s">
-        <v>431</v>
       </c>
       <c r="F103" s="8" t="s">
         <v>22</v>
@@ -6144,19 +6848,19 @@
     </row>
     <row r="104" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" s="6" t="s">
         <v>432</v>
       </c>
-      <c r="B104" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C104" s="6" t="s">
+      <c r="D104" s="6" t="s">
         <v>433</v>
       </c>
-      <c r="D104" s="6" t="s">
+      <c r="E104" s="6" t="s">
         <v>434</v>
-      </c>
-      <c r="E104" s="6" t="s">
-        <v>435</v>
       </c>
       <c r="F104" s="8" t="s">
         <v>22</v>
@@ -6179,10 +6883,10 @@
     </row>
     <row r="105" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B105" s="7" t="s">
         <v>436</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>437</v>
@@ -6191,7 +6895,7 @@
         <v>438</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>285</v>
+        <v>439</v>
       </c>
       <c r="F105" s="8" t="s">
         <v>22</v>
@@ -6214,19 +6918,19 @@
     </row>
     <row r="106" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F106" s="8" t="s">
         <v>22</v>
@@ -6249,19 +6953,19 @@
     </row>
     <row r="107" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F107" s="8" t="s">
         <v>22</v>
@@ -6284,10 +6988,10 @@
     </row>
     <row r="108" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
-        <v>447</v>
-      </c>
-      <c r="B108" s="7" t="s">
         <v>448</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>449</v>
@@ -6391,17 +7095,17 @@
       <c r="A111" s="6" t="s">
         <v>460</v>
       </c>
-      <c r="B111" s="7" t="s">
+      <c r="B111" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" s="6" t="s">
         <v>461</v>
       </c>
-      <c r="C111" s="6" t="s">
+      <c r="D111" s="6" t="s">
         <v>462</v>
       </c>
-      <c r="D111" s="6" t="s">
+      <c r="E111" s="6" t="s">
         <v>463</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>464</v>
       </c>
       <c r="F111" s="8" t="s">
         <v>22</v>
@@ -6424,19 +7128,19 @@
     </row>
     <row r="112" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="B112" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C112" s="6" t="s">
+      <c r="D112" s="6" t="s">
         <v>466</v>
       </c>
-      <c r="D112" s="6" t="s">
+      <c r="E112" s="6" t="s">
         <v>467</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>468</v>
       </c>
       <c r="F112" s="8" t="s">
         <v>22</v>
@@ -6459,10 +7163,10 @@
     </row>
     <row r="113" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="B113" s="7" t="s">
         <v>469</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>24</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>470</v>
@@ -6531,17 +7235,17 @@
       <c r="A115" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="B115" s="7" t="s">
+      <c r="B115" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="D115" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="D115" s="6" t="s">
+      <c r="E115" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>481</v>
       </c>
       <c r="F115" s="8" t="s">
         <v>22</v>
@@ -6564,19 +7268,19 @@
     </row>
     <row r="116" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="B116" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C116" s="6" t="s">
+      <c r="D116" s="6" t="s">
         <v>483</v>
       </c>
-      <c r="D116" s="6" t="s">
+      <c r="E116" s="6" t="s">
         <v>484</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>485</v>
       </c>
       <c r="F116" s="8" t="s">
         <v>22</v>
@@ -6599,19 +7303,19 @@
     </row>
     <row r="117" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C117" s="6" t="s">
         <v>486</v>
       </c>
-      <c r="B117" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C117" s="6" t="s">
+      <c r="D117" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="D117" s="6" t="s">
+      <c r="E117" s="6" t="s">
         <v>488</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>489</v>
       </c>
       <c r="F117" s="8" t="s">
         <v>22</v>
@@ -6634,19 +7338,19 @@
     </row>
     <row r="118" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C118" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="B118" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C118" s="6" t="s">
+      <c r="D118" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="E118" s="6" t="s">
         <v>492</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>493</v>
       </c>
       <c r="F118" s="8" t="s">
         <v>22</v>
@@ -6669,19 +7373,19 @@
     </row>
     <row r="119" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C119" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="B119" s="7" t="s">
+      <c r="D119" s="6" t="s">
         <v>495</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="E119" s="6" t="s">
         <v>496</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>498</v>
       </c>
       <c r="F119" s="8" t="s">
         <v>22</v>
@@ -6704,19 +7408,19 @@
     </row>
     <row r="120" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="D120" s="6" t="s">
         <v>499</v>
       </c>
-      <c r="B120" s="7" t="s">
+      <c r="E120" s="6" t="s">
         <v>500</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>501</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>503</v>
       </c>
       <c r="F120" s="8" t="s">
         <v>22</v>
@@ -6739,19 +7443,19 @@
     </row>
     <row r="121" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="E121" s="6" t="s">
         <v>504</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>506</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>507</v>
       </c>
       <c r="F121" s="8" t="s">
         <v>22</v>
@@ -6774,19 +7478,19 @@
     </row>
     <row r="122" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="D122" s="6" t="s">
         <v>508</v>
       </c>
-      <c r="B122" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C122" s="6" t="s">
+      <c r="E122" s="6" t="s">
         <v>509</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>510</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>511</v>
       </c>
       <c r="F122" s="8" t="s">
         <v>22</v>
@@ -6807,14 +7511,2044 @@
         <v>24</v>
       </c>
     </row>
-    <row r="124" ht="25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
+    <row r="123" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A123" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="D123" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="B124" s="4"/>
-      <c r="C124" s="4"/>
-      <c r="D124" s="4"/>
-      <c r="E124" s="4"/>
+      <c r="E123" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
+      <c r="K123" s="9"/>
+      <c r="L123" s="9"/>
+      <c r="M123" s="9"/>
+      <c r="N123" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O123" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A124" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G124" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H124" s="9"/>
+      <c r="I124" s="9"/>
+      <c r="J124" s="9"/>
+      <c r="K124" s="9"/>
+      <c r="L124" s="9"/>
+      <c r="M124" s="9"/>
+      <c r="N124" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A125" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H125" s="9"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="9"/>
+      <c r="K125" s="9"/>
+      <c r="L125" s="9"/>
+      <c r="M125" s="9"/>
+      <c r="N125" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O125" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A126" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G126" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H126" s="9"/>
+      <c r="I126" s="9"/>
+      <c r="J126" s="9"/>
+      <c r="K126" s="9"/>
+      <c r="L126" s="9"/>
+      <c r="M126" s="9"/>
+      <c r="N126" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O126" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A127" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H127" s="9"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="9"/>
+      <c r="K127" s="9"/>
+      <c r="L127" s="9"/>
+      <c r="M127" s="9"/>
+      <c r="N127" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O127" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A128" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G128" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H128" s="9"/>
+      <c r="I128" s="9"/>
+      <c r="J128" s="9"/>
+      <c r="K128" s="9"/>
+      <c r="L128" s="9"/>
+      <c r="M128" s="9"/>
+      <c r="N128" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O128" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A129" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H129" s="9"/>
+      <c r="I129" s="9"/>
+      <c r="J129" s="9"/>
+      <c r="K129" s="9"/>
+      <c r="L129" s="9"/>
+      <c r="M129" s="9"/>
+      <c r="N129" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O129" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G130" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H130" s="9"/>
+      <c r="I130" s="9"/>
+      <c r="J130" s="9"/>
+      <c r="K130" s="9"/>
+      <c r="L130" s="9"/>
+      <c r="M130" s="9"/>
+      <c r="N130" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O130" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A131" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H131" s="9"/>
+      <c r="I131" s="9"/>
+      <c r="J131" s="9"/>
+      <c r="K131" s="9"/>
+      <c r="L131" s="9"/>
+      <c r="M131" s="9"/>
+      <c r="N131" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O131" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A132" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G132" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H132" s="9"/>
+      <c r="I132" s="9"/>
+      <c r="J132" s="9"/>
+      <c r="K132" s="9"/>
+      <c r="L132" s="9"/>
+      <c r="M132" s="9"/>
+      <c r="N132" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O132" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A133" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H133" s="9"/>
+      <c r="I133" s="9"/>
+      <c r="J133" s="9"/>
+      <c r="K133" s="9"/>
+      <c r="L133" s="9"/>
+      <c r="M133" s="9"/>
+      <c r="N133" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O133" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A134" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G134" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H134" s="9"/>
+      <c r="I134" s="9"/>
+      <c r="J134" s="9"/>
+      <c r="K134" s="9"/>
+      <c r="L134" s="9"/>
+      <c r="M134" s="9"/>
+      <c r="N134" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O134" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A135" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H135" s="9"/>
+      <c r="I135" s="9"/>
+      <c r="J135" s="9"/>
+      <c r="K135" s="9"/>
+      <c r="L135" s="9"/>
+      <c r="M135" s="9"/>
+      <c r="N135" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O135" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A136" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G136" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H136" s="9"/>
+      <c r="I136" s="9"/>
+      <c r="J136" s="9"/>
+      <c r="K136" s="9"/>
+      <c r="L136" s="9"/>
+      <c r="M136" s="9"/>
+      <c r="N136" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O136" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A137" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H137" s="9"/>
+      <c r="I137" s="9"/>
+      <c r="J137" s="9"/>
+      <c r="K137" s="9"/>
+      <c r="L137" s="9"/>
+      <c r="M137" s="9"/>
+      <c r="N137" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O137" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A138" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="F138" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G138" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H138" s="9"/>
+      <c r="I138" s="9"/>
+      <c r="J138" s="9"/>
+      <c r="K138" s="9"/>
+      <c r="L138" s="9"/>
+      <c r="M138" s="9"/>
+      <c r="N138" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O138" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A139" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="F139" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H139" s="9"/>
+      <c r="I139" s="9"/>
+      <c r="J139" s="9"/>
+      <c r="K139" s="9"/>
+      <c r="L139" s="9"/>
+      <c r="M139" s="9"/>
+      <c r="N139" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O139" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A140" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="F140" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G140" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H140" s="9"/>
+      <c r="I140" s="9"/>
+      <c r="J140" s="9"/>
+      <c r="K140" s="9"/>
+      <c r="L140" s="9"/>
+      <c r="M140" s="9"/>
+      <c r="N140" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O140" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A141" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B141" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="F141" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H141" s="9"/>
+      <c r="I141" s="9"/>
+      <c r="J141" s="9"/>
+      <c r="K141" s="9"/>
+      <c r="L141" s="9"/>
+      <c r="M141" s="9"/>
+      <c r="N141" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O141" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A142" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="F142" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G142" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H142" s="9"/>
+      <c r="I142" s="9"/>
+      <c r="J142" s="9"/>
+      <c r="K142" s="9"/>
+      <c r="L142" s="9"/>
+      <c r="M142" s="9"/>
+      <c r="N142" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O142" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A143" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="F143" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H143" s="9"/>
+      <c r="I143" s="9"/>
+      <c r="J143" s="9"/>
+      <c r="K143" s="9"/>
+      <c r="L143" s="9"/>
+      <c r="M143" s="9"/>
+      <c r="N143" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O143" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A144" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="F144" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G144" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H144" s="9"/>
+      <c r="I144" s="9"/>
+      <c r="J144" s="9"/>
+      <c r="K144" s="9"/>
+      <c r="L144" s="9"/>
+      <c r="M144" s="9"/>
+      <c r="N144" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O144" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A145" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="B145" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="F145" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H145" s="9"/>
+      <c r="I145" s="9"/>
+      <c r="J145" s="9"/>
+      <c r="K145" s="9"/>
+      <c r="L145" s="9"/>
+      <c r="M145" s="9"/>
+      <c r="N145" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O145" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A146" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="F146" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G146" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H146" s="9"/>
+      <c r="I146" s="9"/>
+      <c r="J146" s="9"/>
+      <c r="K146" s="9"/>
+      <c r="L146" s="9"/>
+      <c r="M146" s="9"/>
+      <c r="N146" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O146" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A147" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="F147" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H147" s="9"/>
+      <c r="I147" s="9"/>
+      <c r="J147" s="9"/>
+      <c r="K147" s="9"/>
+      <c r="L147" s="9"/>
+      <c r="M147" s="9"/>
+      <c r="N147" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O147" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A148" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="F148" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G148" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H148" s="9"/>
+      <c r="I148" s="9"/>
+      <c r="J148" s="9"/>
+      <c r="K148" s="9"/>
+      <c r="L148" s="9"/>
+      <c r="M148" s="9"/>
+      <c r="N148" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O148" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A149" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="F149" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G149" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H149" s="9"/>
+      <c r="I149" s="9"/>
+      <c r="J149" s="9"/>
+      <c r="K149" s="9"/>
+      <c r="L149" s="9"/>
+      <c r="M149" s="9"/>
+      <c r="N149" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O149" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="F150" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G150" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H150" s="9"/>
+      <c r="I150" s="9"/>
+      <c r="J150" s="9"/>
+      <c r="K150" s="9"/>
+      <c r="L150" s="9"/>
+      <c r="M150" s="9"/>
+      <c r="N150" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O150" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="F151" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H151" s="9"/>
+      <c r="I151" s="9"/>
+      <c r="J151" s="9"/>
+      <c r="K151" s="9"/>
+      <c r="L151" s="9"/>
+      <c r="M151" s="9"/>
+      <c r="N151" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O151" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="F152" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G152" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H152" s="9"/>
+      <c r="I152" s="9"/>
+      <c r="J152" s="9"/>
+      <c r="K152" s="9"/>
+      <c r="L152" s="9"/>
+      <c r="M152" s="9"/>
+      <c r="N152" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O152" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A153" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="F153" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H153" s="9"/>
+      <c r="I153" s="9"/>
+      <c r="J153" s="9"/>
+      <c r="K153" s="9"/>
+      <c r="L153" s="9"/>
+      <c r="M153" s="9"/>
+      <c r="N153" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O153" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A154" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="F154" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G154" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H154" s="9"/>
+      <c r="I154" s="9"/>
+      <c r="J154" s="9"/>
+      <c r="K154" s="9"/>
+      <c r="L154" s="9"/>
+      <c r="M154" s="9"/>
+      <c r="N154" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O154" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A155" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H155" s="9"/>
+      <c r="I155" s="9"/>
+      <c r="J155" s="9"/>
+      <c r="K155" s="9"/>
+      <c r="L155" s="9"/>
+      <c r="M155" s="9"/>
+      <c r="N155" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O155" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A156" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="F156" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G156" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H156" s="9"/>
+      <c r="I156" s="9"/>
+      <c r="J156" s="9"/>
+      <c r="K156" s="9"/>
+      <c r="L156" s="9"/>
+      <c r="M156" s="9"/>
+      <c r="N156" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O156" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A157" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G157" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H157" s="9"/>
+      <c r="I157" s="9"/>
+      <c r="J157" s="9"/>
+      <c r="K157" s="9"/>
+      <c r="L157" s="9"/>
+      <c r="M157" s="9"/>
+      <c r="N157" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O157" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A158" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G158" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H158" s="9"/>
+      <c r="I158" s="9"/>
+      <c r="J158" s="9"/>
+      <c r="K158" s="9"/>
+      <c r="L158" s="9"/>
+      <c r="M158" s="9"/>
+      <c r="N158" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O158" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A159" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="F159" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H159" s="9"/>
+      <c r="I159" s="9"/>
+      <c r="J159" s="9"/>
+      <c r="K159" s="9"/>
+      <c r="L159" s="9"/>
+      <c r="M159" s="9"/>
+      <c r="N159" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O159" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A160" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="F160" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G160" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H160" s="9"/>
+      <c r="I160" s="9"/>
+      <c r="J160" s="9"/>
+      <c r="K160" s="9"/>
+      <c r="L160" s="9"/>
+      <c r="M160" s="9"/>
+      <c r="N160" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O160" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A161" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H161" s="9"/>
+      <c r="I161" s="9"/>
+      <c r="J161" s="9"/>
+      <c r="K161" s="9"/>
+      <c r="L161" s="9"/>
+      <c r="M161" s="9"/>
+      <c r="N161" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O161" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A162" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="F162" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G162" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H162" s="9"/>
+      <c r="I162" s="9"/>
+      <c r="J162" s="9"/>
+      <c r="K162" s="9"/>
+      <c r="L162" s="9"/>
+      <c r="M162" s="9"/>
+      <c r="N162" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O162" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A163" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H163" s="9"/>
+      <c r="I163" s="9"/>
+      <c r="J163" s="9"/>
+      <c r="K163" s="9"/>
+      <c r="L163" s="9"/>
+      <c r="M163" s="9"/>
+      <c r="N163" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O163" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A164" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="F164" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G164" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H164" s="9"/>
+      <c r="I164" s="9"/>
+      <c r="J164" s="9"/>
+      <c r="K164" s="9"/>
+      <c r="L164" s="9"/>
+      <c r="M164" s="9"/>
+      <c r="N164" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O164" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A165" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="D165" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="F165" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G165" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H165" s="9"/>
+      <c r="I165" s="9"/>
+      <c r="J165" s="9"/>
+      <c r="K165" s="9"/>
+      <c r="L165" s="9"/>
+      <c r="M165" s="9"/>
+      <c r="N165" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O165" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="166" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A166" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="B166" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="D166" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="E166" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="F166" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G166" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H166" s="9"/>
+      <c r="I166" s="9"/>
+      <c r="J166" s="9"/>
+      <c r="K166" s="9"/>
+      <c r="L166" s="9"/>
+      <c r="M166" s="9"/>
+      <c r="N166" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O166" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="167" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A167" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="B167" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="D167" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="F167" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H167" s="9"/>
+      <c r="I167" s="9"/>
+      <c r="J167" s="9"/>
+      <c r="K167" s="9"/>
+      <c r="L167" s="9"/>
+      <c r="M167" s="9"/>
+      <c r="N167" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O167" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="168" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A168" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="D168" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="E168" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="F168" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G168" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H168" s="9"/>
+      <c r="I168" s="9"/>
+      <c r="J168" s="9"/>
+      <c r="K168" s="9"/>
+      <c r="L168" s="9"/>
+      <c r="M168" s="9"/>
+      <c r="N168" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O168" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="169" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A169" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="D169" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="E169" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="F169" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H169" s="9"/>
+      <c r="I169" s="9"/>
+      <c r="J169" s="9"/>
+      <c r="K169" s="9"/>
+      <c r="L169" s="9"/>
+      <c r="M169" s="9"/>
+      <c r="N169" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O169" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="170" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A170" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="B170" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D170" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="E170" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="F170" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G170" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H170" s="9"/>
+      <c r="I170" s="9"/>
+      <c r="J170" s="9"/>
+      <c r="K170" s="9"/>
+      <c r="L170" s="9"/>
+      <c r="M170" s="9"/>
+      <c r="N170" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O170" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="171" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A171" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="B171" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="D171" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E171" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="F171" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H171" s="9"/>
+      <c r="I171" s="9"/>
+      <c r="J171" s="9"/>
+      <c r="K171" s="9"/>
+      <c r="L171" s="9"/>
+      <c r="M171" s="9"/>
+      <c r="N171" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O171" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="172" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A172" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B172" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="D172" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="E172" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="F172" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G172" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H172" s="9"/>
+      <c r="I172" s="9"/>
+      <c r="J172" s="9"/>
+      <c r="K172" s="9"/>
+      <c r="L172" s="9"/>
+      <c r="M172" s="9"/>
+      <c r="N172" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O172" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="173" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A173" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B173" s="7" t="s">
+        <v>714</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="D173" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="E173" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="F173" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H173" s="9"/>
+      <c r="I173" s="9"/>
+      <c r="J173" s="9"/>
+      <c r="K173" s="9"/>
+      <c r="L173" s="9"/>
+      <c r="M173" s="9"/>
+      <c r="N173" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O173" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A174" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B174" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="D174" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="E174" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="F174" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G174" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H174" s="9"/>
+      <c r="I174" s="9"/>
+      <c r="J174" s="9"/>
+      <c r="K174" s="9"/>
+      <c r="L174" s="9"/>
+      <c r="M174" s="9"/>
+      <c r="N174" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O174" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="175" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A175" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="B175" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="D175" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="E175" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="F175" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H175" s="9"/>
+      <c r="I175" s="9"/>
+      <c r="J175" s="9"/>
+      <c r="K175" s="9"/>
+      <c r="L175" s="9"/>
+      <c r="M175" s="9"/>
+      <c r="N175" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O175" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="176" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A176" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="D176" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="E176" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="F176" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H176" s="9"/>
+      <c r="I176" s="9"/>
+      <c r="J176" s="9"/>
+      <c r="K176" s="9"/>
+      <c r="L176" s="9"/>
+      <c r="M176" s="9"/>
+      <c r="N176" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O176" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="177" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A177" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="B177" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="D177" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="E177" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="F177" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H177" s="9"/>
+      <c r="I177" s="9"/>
+      <c r="J177" s="9"/>
+      <c r="K177" s="9"/>
+      <c r="L177" s="9"/>
+      <c r="M177" s="9"/>
+      <c r="N177" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O177" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="178" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A178" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="B178" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="D178" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="E178" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="F178" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G178" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H178" s="9"/>
+      <c r="I178" s="9"/>
+      <c r="J178" s="9"/>
+      <c r="K178" s="9"/>
+      <c r="L178" s="9"/>
+      <c r="M178" s="9"/>
+      <c r="N178" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O178" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="179" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A179" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="B179" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="D179" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="E179" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="F179" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H179" s="9"/>
+      <c r="I179" s="9"/>
+      <c r="J179" s="9"/>
+      <c r="K179" s="9"/>
+      <c r="L179" s="9"/>
+      <c r="M179" s="9"/>
+      <c r="N179" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O179" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="180" ht="55" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A180" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="B180" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="D180" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="E180" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="F180" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G180" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H180" s="9"/>
+      <c r="I180" s="9"/>
+      <c r="J180" s="9"/>
+      <c r="K180" s="9"/>
+      <c r="L180" s="9"/>
+      <c r="M180" s="9"/>
+      <c r="N180" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O180" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="182" ht="25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="B182" s="4"/>
+      <c r="C182" s="4"/>
+      <c r="D182" s="4"/>
+      <c r="E182" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -6824,31 +9558,31 @@
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A124:E124"/>
+    <mergeCell ref="A182:E182"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select PASS, FAIL, N/A, or BLOCKED" sqref="H10:H122">
+    <dataValidation type="list" allowBlank="1" sqref="H10:H180">
       <formula1>"PASS,FAIL,N/A,BLOCKED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select PASS, FAIL, N/A, or BLOCKED" sqref="H4:H122">
+    <dataValidation type="list" allowBlank="1" sqref="H4:H180">
       <formula1>"PASS,FAIL,N/A,BLOCKED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select PASS, FAIL, N/A, or BLOCKED" sqref="J10:J122">
+    <dataValidation type="list" allowBlank="1" sqref="J10:J180">
       <formula1>"PASS,FAIL,N/A,BLOCKED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select PASS, FAIL, N/A, or BLOCKED" sqref="J4:J122">
+    <dataValidation type="list" allowBlank="1" sqref="J4:J180">
       <formula1>"PASS,FAIL,N/A,BLOCKED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select PASS, FAIL, N/A, or BLOCKED" sqref="L10:L122">
+    <dataValidation type="list" allowBlank="1" sqref="L10:L180">
       <formula1>"PASS,FAIL,N/A,BLOCKED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select PASS, FAIL, N/A, or BLOCKED" sqref="L4:L122">
+    <dataValidation type="list" allowBlank="1" sqref="L4:L180">
       <formula1>"PASS,FAIL,N/A,BLOCKED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select APPROVED, REJECTED, or PENDING" sqref="N10:N122">
+    <dataValidation type="list" allowBlank="1" sqref="N10:N180">
       <formula1>"APPROVED,REJECTED,PENDING"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="Invalid" error="Please select APPROVED, REJECTED, or PENDING" sqref="N4:N122">
+    <dataValidation type="list" allowBlank="1" sqref="N4:N180">
       <formula1>"APPROVED,REJECTED,PENDING"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6878,7 +9612,7 @@
   <sheetData>
     <row r="1" ht="35" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>513</v>
+        <v>748</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -6894,45 +9628,45 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>514</v>
+        <v>749</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>515</v>
+        <v>750</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>516</v>
+        <v>751</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>517</v>
+        <v>752</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>518</v>
+        <v>753</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>519</v>
+        <v>754</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>520</v>
+        <v>755</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>521</v>
+        <v>756</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>522</v>
+        <v>757</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>523</v>
+        <v>758</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>524</v>
+        <v>759</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>525</v>
+        <v>760</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>526</v>
+        <v>761</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -6948,7 +9682,7 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>527</v>
+        <v>762</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -6964,7 +9698,7 @@
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>528</v>
+        <v>763</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -6980,7 +9714,7 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>529</v>
+        <v>764</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -6996,7 +9730,7 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>530</v>
+        <v>765</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7012,7 +9746,7 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>531</v>
+        <v>766</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -7028,7 +9762,7 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>532</v>
+        <v>767</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -7044,7 +9778,7 @@
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>533</v>
+        <v>768</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -7060,7 +9794,7 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>534</v>
+        <v>769</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -7076,7 +9810,7 @@
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>535</v>
+        <v>770</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -7092,7 +9826,7 @@
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>536</v>
+        <v>771</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -7108,7 +9842,7 @@
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>537</v>
+        <v>772</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -7124,7 +9858,7 @@
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>538</v>
+        <v>773</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -7140,7 +9874,7 @@
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>539</v>
+        <v>774</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -7156,7 +9890,7 @@
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>540</v>
+        <v>775</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -7172,7 +9906,7 @@
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>541</v>
+        <v>776</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -7188,7 +9922,7 @@
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>542</v>
+        <v>777</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -7204,7 +9938,7 @@
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>543</v>
+        <v>778</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -7220,7 +9954,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>544</v>
+        <v>779</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -7236,7 +9970,7 @@
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>545</v>
+        <v>780</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -7252,7 +9986,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>546</v>
+        <v>781</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -7268,7 +10002,7 @@
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>547</v>
+        <v>782</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -7284,7 +10018,7 @@
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>548</v>
+        <v>783</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -7300,7 +10034,7 @@
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>549</v>
+        <v>784</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -7316,7 +10050,7 @@
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>550</v>
+        <v>785</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -7332,7 +10066,7 @@
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>551</v>
+        <v>786</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -7348,7 +10082,7 @@
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>552</v>
+        <v>787</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -7364,7 +10098,7 @@
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>553</v>
+        <v>788</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -7380,7 +10114,7 @@
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>554</v>
+        <v>789</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -7396,7 +10130,7 @@
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>555</v>
+        <v>790</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -7412,7 +10146,7 @@
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>556</v>
+        <v>791</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -7428,7 +10162,7 @@
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>557</v>
+        <v>792</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -7444,7 +10178,7 @@
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>558</v>
+        <v>793</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -7460,7 +10194,7 @@
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>559</v>
+        <v>794</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -7476,7 +10210,7 @@
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>560</v>
+        <v>795</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -7492,7 +10226,7 @@
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>561</v>
+        <v>796</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -7508,7 +10242,7 @@
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>562</v>
+        <v>797</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -7524,7 +10258,7 @@
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>563</v>
+        <v>798</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -7540,7 +10274,7 @@
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>564</v>
+        <v>799</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -7556,7 +10290,7 @@
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>565</v>
+        <v>800</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -7572,7 +10306,7 @@
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>566</v>
+        <v>801</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -7588,7 +10322,7 @@
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>567</v>
+        <v>802</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -7604,7 +10338,7 @@
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>568</v>
+        <v>803</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -7620,7 +10354,7 @@
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>569</v>
+        <v>804</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -7636,7 +10370,7 @@
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>570</v>
+        <v>805</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -7652,7 +10386,7 @@
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>571</v>
+        <v>806</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -7668,7 +10402,7 @@
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>572</v>
+        <v>807</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -7684,7 +10418,7 @@
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>573</v>
+        <v>808</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -7700,7 +10434,7 @@
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>574</v>
+        <v>809</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -7716,7 +10450,7 @@
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>575</v>
+        <v>810</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -7742,10 +10476,10 @@
       <formula1>"Critical,High,Medium,Low,Nice-to-Have"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E10:E52">
-      <formula1>"POS,Receipts,Day-End,Search,Enquiries,Deposits,Supervisor,Reports,Debt/Legal,General"</formula1>
+      <formula1>"POS,Cashier Setup,Day-End,Supervisor,Receipts,Search,Enquiries,Deposits,Reports,Debt/Legal,General"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E3:E52">
-      <formula1>"POS,Receipts,Day-End,Search,Enquiries,Deposits,Supervisor,Reports,Debt/Legal,General"</formula1>
+      <formula1>"POS,Cashier Setup,Day-End,Supervisor,Receipts,Search,Enquiries,Deposits,Reports,Debt/Legal,General"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="I10:I52">
       <formula1>"New,Under Review,Approved,In Progress,Completed,Deferred,Rejected"</formula1>
@@ -7781,7 +10515,7 @@
   <sheetData>
     <row r="1" ht="35" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>576</v>
+        <v>811</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -7799,51 +10533,51 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>577</v>
+        <v>812</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>578</v>
+        <v>813</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>579</v>
+        <v>814</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>580</v>
+        <v>815</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>518</v>
+        <v>753</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>581</v>
+        <v>816</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>582</v>
+        <v>817</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>583</v>
+        <v>818</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>584</v>
+        <v>819</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>522</v>
+        <v>757</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>523</v>
+        <v>758</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>585</v>
+        <v>820</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>586</v>
+        <v>821</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>587</v>
+        <v>822</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -7861,7 +10595,7 @@
     </row>
     <row r="4" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>588</v>
+        <v>823</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -7879,7 +10613,7 @@
     </row>
     <row r="5" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>589</v>
+        <v>824</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -7897,7 +10631,7 @@
     </row>
     <row r="6" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>590</v>
+        <v>825</v>
       </c>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -7915,7 +10649,7 @@
     </row>
     <row r="7" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>591</v>
+        <v>826</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -7933,7 +10667,7 @@
     </row>
     <row r="8" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>592</v>
+        <v>827</v>
       </c>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -7951,7 +10685,7 @@
     </row>
     <row r="9" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>593</v>
+        <v>828</v>
       </c>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -7969,7 +10703,7 @@
     </row>
     <row r="10" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>594</v>
+        <v>829</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -7987,7 +10721,7 @@
     </row>
     <row r="11" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>595</v>
+        <v>830</v>
       </c>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -8005,7 +10739,7 @@
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>596</v>
+        <v>831</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -8023,7 +10757,7 @@
     </row>
     <row r="13" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>597</v>
+        <v>832</v>
       </c>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -8041,7 +10775,7 @@
     </row>
     <row r="14" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>598</v>
+        <v>833</v>
       </c>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -8059,7 +10793,7 @@
     </row>
     <row r="15" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>599</v>
+        <v>834</v>
       </c>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -8077,7 +10811,7 @@
     </row>
     <row r="16" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>600</v>
+        <v>835</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -8095,7 +10829,7 @@
     </row>
     <row r="17" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>601</v>
+        <v>836</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -8113,7 +10847,7 @@
     </row>
     <row r="18" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>602</v>
+        <v>837</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -8131,7 +10865,7 @@
     </row>
     <row r="19" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>603</v>
+        <v>838</v>
       </c>
       <c r="B19" s="6"/>
       <c r="C19" s="6"/>
@@ -8149,7 +10883,7 @@
     </row>
     <row r="20" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>604</v>
+        <v>839</v>
       </c>
       <c r="B20" s="6"/>
       <c r="C20" s="6"/>
@@ -8167,7 +10901,7 @@
     </row>
     <row r="21" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>605</v>
+        <v>840</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -8185,7 +10919,7 @@
     </row>
     <row r="22" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>606</v>
+        <v>841</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6"/>
@@ -8203,7 +10937,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>607</v>
+        <v>842</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -8221,7 +10955,7 @@
     </row>
     <row r="24" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>608</v>
+        <v>843</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -8239,7 +10973,7 @@
     </row>
     <row r="25" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
-        <v>609</v>
+        <v>844</v>
       </c>
       <c r="B25" s="6"/>
       <c r="C25" s="6"/>
@@ -8257,7 +10991,7 @@
     </row>
     <row r="26" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>610</v>
+        <v>845</v>
       </c>
       <c r="B26" s="6"/>
       <c r="C26" s="6"/>
@@ -8275,7 +11009,7 @@
     </row>
     <row r="27" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>611</v>
+        <v>846</v>
       </c>
       <c r="B27" s="6"/>
       <c r="C27" s="6"/>
@@ -8293,7 +11027,7 @@
     </row>
     <row r="28" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>612</v>
+        <v>847</v>
       </c>
       <c r="B28" s="6"/>
       <c r="C28" s="6"/>
@@ -8311,7 +11045,7 @@
     </row>
     <row r="29" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>613</v>
+        <v>848</v>
       </c>
       <c r="B29" s="6"/>
       <c r="C29" s="6"/>
@@ -8329,7 +11063,7 @@
     </row>
     <row r="30" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>614</v>
+        <v>849</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -8347,7 +11081,7 @@
     </row>
     <row r="31" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>615</v>
+        <v>850</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -8365,7 +11099,7 @@
     </row>
     <row r="32" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>616</v>
+        <v>851</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -8383,7 +11117,7 @@
     </row>
     <row r="33" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
-        <v>617</v>
+        <v>852</v>
       </c>
       <c r="B33" s="6"/>
       <c r="C33" s="6"/>
@@ -8401,7 +11135,7 @@
     </row>
     <row r="34" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>618</v>
+        <v>853</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -8419,7 +11153,7 @@
     </row>
     <row r="35" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
-        <v>619</v>
+        <v>854</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -8437,7 +11171,7 @@
     </row>
     <row r="36" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>620</v>
+        <v>855</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -8455,7 +11189,7 @@
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>621</v>
+        <v>856</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6"/>
@@ -8473,7 +11207,7 @@
     </row>
     <row r="38" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>622</v>
+        <v>857</v>
       </c>
       <c r="B38" s="6"/>
       <c r="C38" s="6"/>
@@ -8491,7 +11225,7 @@
     </row>
     <row r="39" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
-        <v>623</v>
+        <v>858</v>
       </c>
       <c r="B39" s="6"/>
       <c r="C39" s="6"/>
@@ -8509,7 +11243,7 @@
     </row>
     <row r="40" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>624</v>
+        <v>859</v>
       </c>
       <c r="B40" s="6"/>
       <c r="C40" s="6"/>
@@ -8527,7 +11261,7 @@
     </row>
     <row r="41" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
-        <v>625</v>
+        <v>860</v>
       </c>
       <c r="B41" s="6"/>
       <c r="C41" s="6"/>
@@ -8545,7 +11279,7 @@
     </row>
     <row r="42" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>626</v>
+        <v>861</v>
       </c>
       <c r="B42" s="6"/>
       <c r="C42" s="6"/>
@@ -8563,7 +11297,7 @@
     </row>
     <row r="43" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
-        <v>627</v>
+        <v>862</v>
       </c>
       <c r="B43" s="6"/>
       <c r="C43" s="6"/>
@@ -8581,7 +11315,7 @@
     </row>
     <row r="44" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>628</v>
+        <v>863</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -8599,7 +11333,7 @@
     </row>
     <row r="45" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
-        <v>629</v>
+        <v>864</v>
       </c>
       <c r="B45" s="6"/>
       <c r="C45" s="6"/>
@@ -8617,7 +11351,7 @@
     </row>
     <row r="46" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>630</v>
+        <v>865</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -8635,7 +11369,7 @@
     </row>
     <row r="47" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
-        <v>631</v>
+        <v>866</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -8653,7 +11387,7 @@
     </row>
     <row r="48" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
-        <v>632</v>
+        <v>867</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -8671,7 +11405,7 @@
     </row>
     <row r="49" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
-        <v>633</v>
+        <v>868</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -8689,7 +11423,7 @@
     </row>
     <row r="50" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>634</v>
+        <v>869</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6"/>
@@ -8707,7 +11441,7 @@
     </row>
     <row r="51" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
-        <v>635</v>
+        <v>870</v>
       </c>
       <c r="B51" s="6"/>
       <c r="C51" s="6"/>
@@ -8725,7 +11459,7 @@
     </row>
     <row r="52" ht="25" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
-        <v>636</v>
+        <v>871</v>
       </c>
       <c r="B52" s="6"/>
       <c r="C52" s="6"/>
@@ -8753,10 +11487,10 @@
       <formula1>"Critical,High,Medium,Low,Cosmetic"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E10:E52">
-      <formula1>"POS,Receipts,Day-End,Search,Enquiries,Deposits,Supervisor,Reports,Debt/Legal,General"</formula1>
+      <formula1>"POS,Cashier Setup,Day-End,Supervisor,Receipts,Search,Enquiries,Deposits,Reports,Debt/Legal,General"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="E3:E52">
-      <formula1>"POS,Receipts,Day-End,Search,Enquiries,Deposits,Supervisor,Reports,Debt/Legal,General"</formula1>
+      <formula1>"POS,Cashier Setup,Day-End,Supervisor,Receipts,Search,Enquiries,Deposits,Reports,Debt/Legal,General"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="K10:K52">
       <formula1>"Open,In Progress,Fixed,Verified,Closed,Won't Fix,Deferred"</formula1>
